--- a/project/model/VAACA-financial-model.xlsx
+++ b/project/model/VAACA-financial-model.xlsx
@@ -20,6 +20,7 @@
     <sheet name="Unit Economics" sheetId="10" state="visible" r:id="rId12"/>
     <sheet name="Revenue Mix" sheetId="11" state="visible" r:id="rId13"/>
     <sheet name="Product Scoring" sheetId="12" state="visible" r:id="rId14"/>
+    <sheet name="Entity Split" sheetId="13" state="visible" r:id="rId15"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="762" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="865" uniqueCount="395">
   <si>
     <t xml:space="preserve">VAACA — Five-year financial model</t>
   </si>
@@ -705,6 +706,15 @@
     <t xml:space="preserve">Unit count × price. Nothing here is typed in.</t>
   </si>
   <si>
+    <t xml:space="preserve">Delivered by</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VAACA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAFN</t>
+  </si>
+  <si>
     <t xml:space="preserve">By engine</t>
   </si>
   <si>
@@ -720,6 +730,9 @@
     <t xml:space="preserve">Targets are §41 and §65–68 of the specification, which calls them planning scenarios rather than forecasts.</t>
   </si>
   <si>
+    <t xml:space="preserve">VAACA is a non-profit and keeps what a non-profit does: its own dues, the forums it convenes, and the licensing of research and intelligence it produced itself. IAFN delivers the services — education, certification, advisory and commissioned research — which is the mandate it already holds as a founding member.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Staffing</t>
   </si>
   <si>
@@ -762,6 +775,9 @@
     <t xml:space="preserve">Cost Year 5</t>
   </si>
   <si>
+    <t xml:space="preserve">Entity</t>
+  </si>
+  <si>
     <t xml:space="preserve">Secretary General</t>
   </si>
   <si>
@@ -807,6 +823,9 @@
     <t xml:space="preserve">Salaries are planning figures for Yaoundé, not offers. Both Year 1 posts are currently vacant.</t>
   </si>
   <si>
+    <t xml:space="preserve">IAFN's own staffing is outside this model. Only the post VAACA would otherwise carry and no longer needs is marked — the education lead.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Costs (XAF)</t>
   </si>
   <si>
@@ -1117,6 +1136,87 @@
   </si>
   <si>
     <t xml:space="preserve">Composite = strategic importance × the mean of institutional value and scalability × gross margin, which is the §44 formula written out. Complexity and the two risk columns are scored but deliberately not multiplied in: they are reasons to sequence a product later or govern it harder, not reasons to drop it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two entities (XAF)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VAACA is the non-profit. IAFN, a founding member, delivers the services. This is what each earns.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenue by entity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VAACA — own activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAFN — services delivered</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ecosystem revenue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAFN share of the ecosystem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What flows back to VAACA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAFN delivers using VAACA's brand, its curriculum, its credential and its member channel. A licence on delivered revenue is what makes that an arrangement rather than a gift.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Licence rate on IAFN delivery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Licence income to VAACA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VAACA total income</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VAACA's own operating result</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Income</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delivery cost it still bears</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cumulative result</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Related-party test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAFN is a founding member of VAACA and its sole service provider. That is a related-party arrangement, and the specification's own 15% concentration ceiling is the right place to test it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAFN licence as share of VAACA income</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The ceiling is the easy test and it passes. The harder one is not arithmetic: IAFN sits in the General Assembly and is named for a seat on the Governing Council, while earning from the ecosystem VAACA convenes. That is governed by recusal and publication, not by a percentage — see project/STRUCTURE.md.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What the structure costs VAACA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deepest cumulative deficit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What VAACA must raise before the structure pays for itself.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First year in surplus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Licence rate that would break even in Year 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Against the 12% modelled. The gap is the question the arrangement has to answer.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moving services to IAFN is right for the mandate and it is not free. VAACA gives up education, certification and advisory — margin-rich lines — and keeps almost all of the fixed cost base: the secretariat, the platform, the chapters. Break-even moves from Year 2 to Year 3 and the funding requirement roughly triples. The licence rate is the lever, and 12% is a placeholder, not a negotiated figure.</t>
   </si>
 </sst>
 </file>
@@ -1276,7 +1376,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="47">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1377,12 +1477,20 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="167" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -1409,40 +1517,12 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -1455,6 +1535,34 @@
     </xf>
     <xf numFmtId="167" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1877,12 +1985,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1890,31 +1998,31 @@
         <v>78</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1947,23 +2055,23 @@
         <f aca="false">IF(G4&gt;=1,0,D4*E4/(1-G4))</f>
         <v>1164739.7318129</v>
       </c>
-      <c r="I4" s="28" t="n">
+      <c r="I4" s="30" t="n">
         <f aca="false">IF(D4*E4=0,0,F4/(D4*E4/12))</f>
         <v>5.61967138810198</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="B5" s="25" t="n">
+      <c r="B5" s="26" t="n">
         <f aca="false">Customers!L10+Customers!L11+Customers!L12</f>
         <v>21</v>
       </c>
-      <c r="C5" s="25" t="n">
+      <c r="C5" s="26" t="n">
         <f aca="false">Revenue!F$42</f>
         <v>117000000</v>
       </c>
@@ -1971,26 +2079,26 @@
         <f aca="false">IF(B5=0,0,C5/B5)</f>
         <v>5571428.57142857</v>
       </c>
-      <c r="E5" s="29" t="n">
+      <c r="E5" s="31" t="n">
         <f aca="false">IF(C5=0,0,1)</f>
         <v>1</v>
       </c>
       <c r="F5" s="19" t="n">
         <v>2500000</v>
       </c>
-      <c r="G5" s="30" t="n">
+      <c r="G5" s="32" t="n">
         <v>0.7</v>
       </c>
       <c r="H5" s="23" t="n">
         <f aca="false">IF(G5&gt;=1,0,D5*E5/(1-G5))</f>
         <v>18571428.5714286</v>
       </c>
-      <c r="I5" s="31" t="n">
+      <c r="I5" s="33" t="n">
         <f aca="false">IF(D5*E5=0,0,F5/(D5*E5/12))</f>
         <v>5.38461538461538</v>
       </c>
       <c r="J5" s="18" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2023,23 +2131,23 @@
         <f aca="false">IF(G6&gt;=1,0,D6*E6/(1-G6))</f>
         <v>1165070.42253521</v>
       </c>
-      <c r="I6" s="28" t="n">
+      <c r="I6" s="30" t="n">
         <f aca="false">IF(D6*E6=0,0,F6/(D6*E6/12))</f>
         <v>2.47195357833656</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="B7" s="25" t="n">
+      <c r="B7" s="26" t="n">
         <f aca="false">Customers!L16+Customers!L17+Customers!L18</f>
         <v>116</v>
       </c>
-      <c r="C7" s="25" t="n">
+      <c r="C7" s="26" t="n">
         <f aca="false">Revenue!F$44</f>
         <v>47850000</v>
       </c>
@@ -2047,26 +2155,26 @@
         <f aca="false">IF(B7=0,0,C7/B7)</f>
         <v>412500</v>
       </c>
-      <c r="E7" s="29" t="n">
+      <c r="E7" s="31" t="n">
         <f aca="false">IF(C7=0,0,1-Costs!E$6/C7)</f>
         <v>0.7</v>
       </c>
       <c r="F7" s="19" t="n">
         <v>90000</v>
       </c>
-      <c r="G7" s="30" t="n">
+      <c r="G7" s="32" t="n">
         <v>0.8</v>
       </c>
       <c r="H7" s="23" t="n">
         <f aca="false">IF(G7&gt;=1,0,D7*E7/(1-G7))</f>
         <v>1443750</v>
       </c>
-      <c r="I7" s="31" t="n">
+      <c r="I7" s="33" t="n">
         <f aca="false">IF(D7*E7=0,0,F7/(D7*E7/12))</f>
         <v>3.74025974025974</v>
       </c>
       <c r="J7" s="18" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2099,23 +2207,23 @@
         <f aca="false">IF(G8&gt;=1,0,D8*E8/(1-G8))</f>
         <v>3763636.36363636</v>
       </c>
-      <c r="I8" s="28" t="n">
+      <c r="I8" s="30" t="n">
         <f aca="false">IF(D8*E8=0,0,F8/(D8*E8/12))</f>
         <v>2.02898550724638</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="B9" s="25" t="n">
+      <c r="B9" s="26" t="n">
         <f aca="false">Customers!L22+Customers!L23+Customers!L24+Customers!L25+Customers!L26</f>
         <v>127</v>
       </c>
-      <c r="C9" s="25" t="n">
+      <c r="C9" s="26" t="n">
         <f aca="false">Revenue!F$46</f>
         <v>76000000</v>
       </c>
@@ -2123,26 +2231,26 @@
         <f aca="false">IF(B9=0,0,C9/B9)</f>
         <v>598425.196850394</v>
       </c>
-      <c r="E9" s="29" t="n">
+      <c r="E9" s="31" t="n">
         <f aca="false">IF(C9=0,0,1)</f>
         <v>1</v>
       </c>
       <c r="F9" s="19" t="n">
         <v>220000</v>
       </c>
-      <c r="G9" s="30" t="n">
+      <c r="G9" s="32" t="n">
         <v>0.82</v>
       </c>
       <c r="H9" s="23" t="n">
         <f aca="false">IF(G9&gt;=1,0,D9*E9/(1-G9))</f>
         <v>3324584.42694663</v>
       </c>
-      <c r="I9" s="31" t="n">
+      <c r="I9" s="33" t="n">
         <f aca="false">IF(D9*E9=0,0,F9/(D9*E9/12))</f>
         <v>4.41157894736842</v>
       </c>
       <c r="J9" s="18" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2175,23 +2283,23 @@
         <f aca="false">IF(G10&gt;=1,0,D10*E10/(1-G10))</f>
         <v>267423.01458671</v>
       </c>
-      <c r="I10" s="28" t="n">
+      <c r="I10" s="30" t="n">
         <f aca="false">IF(D10*E10=0,0,F10/(D10*E10/12))</f>
         <v>3.49010101010101</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="B11" s="25" t="n">
+      <c r="B11" s="26" t="n">
         <f aca="false">Customers!L31+Customers!L32+Customers!L33</f>
         <v>14</v>
       </c>
-      <c r="C11" s="25" t="n">
+      <c r="C11" s="26" t="n">
         <f aca="false">Revenue!F$48</f>
         <v>112000000</v>
       </c>
@@ -2199,26 +2307,26 @@
         <f aca="false">IF(B11=0,0,C11/B11)</f>
         <v>8000000</v>
       </c>
-      <c r="E11" s="29" t="n">
+      <c r="E11" s="31" t="n">
         <f aca="false">IF(C11=0,0,1-Costs!E$8/C11)</f>
         <v>0.56</v>
       </c>
       <c r="F11" s="19" t="n">
         <v>3500000</v>
       </c>
-      <c r="G11" s="30" t="n">
+      <c r="G11" s="32" t="n">
         <v>0.35</v>
       </c>
       <c r="H11" s="23" t="n">
         <f aca="false">IF(G11&gt;=1,0,D11*E11/(1-G11))</f>
         <v>6892307.69230769</v>
       </c>
-      <c r="I11" s="31" t="n">
+      <c r="I11" s="33" t="n">
         <f aca="false">IF(D11*E11=0,0,F11/(D11*E11/12))</f>
         <v>9.375</v>
       </c>
       <c r="J11" s="18" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2251,23 +2359,23 @@
         <f aca="false">IF(G12&gt;=1,0,D12*E12/(1-G12))</f>
         <v>13333333.3333333</v>
       </c>
-      <c r="I12" s="28" t="n">
+      <c r="I12" s="30" t="n">
         <f aca="false">IF(D12*E12=0,0,F12/(D12*E12/12))</f>
         <v>2.4</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="B13" s="25" t="n">
+      <c r="B13" s="26" t="n">
         <f aca="false">Customers!L37+Customers!L38</f>
         <v>112</v>
       </c>
-      <c r="C13" s="25" t="n">
+      <c r="C13" s="26" t="n">
         <f aca="false">Revenue!F$50</f>
         <v>26500000</v>
       </c>
@@ -2275,41 +2383,41 @@
         <f aca="false">IF(B13=0,0,C13/B13)</f>
         <v>236607.142857143</v>
       </c>
-      <c r="E13" s="29" t="n">
+      <c r="E13" s="31" t="n">
         <f aca="false">IF(C13=0,0,1)</f>
         <v>1</v>
       </c>
       <c r="F13" s="19" t="n">
         <v>60000</v>
       </c>
-      <c r="G13" s="30" t="n">
+      <c r="G13" s="32" t="n">
         <v>0.8</v>
       </c>
       <c r="H13" s="23" t="n">
         <f aca="false">IF(G13&gt;=1,0,D13*E13/(1-G13))</f>
         <v>1183035.71428571</v>
       </c>
-      <c r="I13" s="31" t="n">
+      <c r="I13" s="33" t="n">
         <f aca="false">IF(D13*E13=0,0,F13/(D13*E13/12))</f>
         <v>3.04301886792453</v>
       </c>
       <c r="J13" s="18" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="27" t="s">
-        <v>321</v>
-      </c>
-      <c r="B16" s="27"/>
-      <c r="C16" s="27"/>
-      <c r="D16" s="27"/>
-      <c r="E16" s="27"/>
-      <c r="F16" s="27"/>
-      <c r="G16" s="27"/>
-      <c r="H16" s="27"/>
-      <c r="I16" s="27"/>
-      <c r="J16" s="27"/>
+      <c r="A16" s="29" t="s">
+        <v>327</v>
+      </c>
+      <c r="B16" s="29"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="29"/>
+      <c r="E16" s="29"/>
+      <c r="F16" s="29"/>
+      <c r="G16" s="29"/>
+      <c r="H16" s="29"/>
+      <c r="I16" s="29"/>
+      <c r="J16" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2340,12 +2448,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2369,7 +2477,7 @@
       </c>
       <c r="G3" s="9"/>
       <c r="H3" s="9" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2397,37 +2505,37 @@
         <v>0.221160215766064</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="B5" s="29" t="n">
+      <c r="B5" s="31" t="n">
         <f aca="false">IF(Revenue!D$52=0,0,Revenue!D$42/Revenue!D$52)</f>
         <v>0.200904068307383</v>
       </c>
-      <c r="C5" s="29" t="n">
+      <c r="C5" s="31" t="n">
         <f aca="false">IF(Revenue!E$52=0,0,Revenue!E$42/Revenue!E$52)</f>
         <v>0.121212121212121</v>
       </c>
-      <c r="D5" s="29" t="n">
+      <c r="D5" s="31" t="n">
         <f aca="false">IF(Revenue!F$52=0,0,Revenue!F$42/Revenue!F$52)</f>
         <v>0.110484194622158</v>
       </c>
-      <c r="E5" s="29" t="n">
+      <c r="E5" s="31" t="n">
         <f aca="false">IF(Revenue!G$52=0,0,Revenue!G$42/Revenue!G$52)</f>
         <v>0.0893716485631789</v>
       </c>
-      <c r="F5" s="29" t="n">
+      <c r="F5" s="31" t="n">
         <f aca="false">IF(Revenue!H$52=0,0,Revenue!H$42/Revenue!H$52)</f>
         <v>0.0779786126620611</v>
       </c>
       <c r="G5" s="22"/>
       <c r="H5" s="22"/>
       <c r="I5" s="20" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2455,37 +2563,37 @@
         <v>0.128702564587868</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="B7" s="29" t="n">
+      <c r="B7" s="31" t="n">
         <f aca="false">IF(Revenue!D$52=0,0,Revenue!D$44/Revenue!D$52)</f>
         <v>0</v>
       </c>
-      <c r="C7" s="29" t="n">
+      <c r="C7" s="31" t="n">
         <f aca="false">IF(Revenue!E$52=0,0,Revenue!E$44/Revenue!E$52)</f>
         <v>0.0338266384778013</v>
       </c>
-      <c r="D7" s="29" t="n">
+      <c r="D7" s="31" t="n">
         <f aca="false">IF(Revenue!F$52=0,0,Revenue!F$44/Revenue!F$52)</f>
         <v>0.0451852026723955</v>
       </c>
-      <c r="E7" s="29" t="n">
+      <c r="E7" s="31" t="n">
         <f aca="false">IF(Revenue!G$52=0,0,Revenue!G$44/Revenue!G$52)</f>
         <v>0.0502406159769009</v>
       </c>
-      <c r="F7" s="29" t="n">
+      <c r="F7" s="31" t="n">
         <f aca="false">IF(Revenue!H$52=0,0,Revenue!H$44/Revenue!H$52)</f>
         <v>0.0556449323365194</v>
       </c>
       <c r="G7" s="22"/>
       <c r="H7" s="22"/>
       <c r="I7" s="20" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2513,37 +2621,37 @@
         <v>0.0942557017128797</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="B9" s="29" t="n">
+      <c r="B9" s="31" t="n">
         <f aca="false">IF(Revenue!D$52=0,0,Revenue!D$46/Revenue!D$52)</f>
         <v>0</v>
       </c>
-      <c r="C9" s="29" t="n">
+      <c r="C9" s="31" t="n">
         <f aca="false">IF(Revenue!E$52=0,0,Revenue!E$46/Revenue!E$52)</f>
         <v>0.0526192154099131</v>
       </c>
-      <c r="D9" s="29" t="n">
+      <c r="D9" s="31" t="n">
         <f aca="false">IF(Revenue!F$52=0,0,Revenue!F$46/Revenue!F$52)</f>
         <v>0.0717675110366156</v>
       </c>
-      <c r="E9" s="29" t="n">
+      <c r="E9" s="31" t="n">
         <f aca="false">IF(Revenue!G$52=0,0,Revenue!G$46/Revenue!G$52)</f>
         <v>0.0767221229203905</v>
       </c>
-      <c r="F9" s="29" t="n">
+      <c r="F9" s="31" t="n">
         <f aca="false">IF(Revenue!H$52=0,0,Revenue!H$46/Revenue!H$52)</f>
         <v>0.0861171571874704</v>
       </c>
       <c r="G9" s="22"/>
       <c r="H9" s="22"/>
       <c r="I9" s="20" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2571,37 +2679,37 @@
         <v>0.129081101542538</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="B11" s="29" t="n">
+      <c r="B11" s="31" t="n">
         <f aca="false">IF(Revenue!D$52=0,0,Revenue!D$48/Revenue!D$52)</f>
         <v>0.12054244098443</v>
       </c>
-      <c r="C11" s="29" t="n">
+      <c r="C11" s="31" t="n">
         <f aca="false">IF(Revenue!E$52=0,0,Revenue!E$48/Revenue!E$52)</f>
         <v>0.105238430819826</v>
       </c>
-      <c r="D11" s="29" t="n">
+      <c r="D11" s="31" t="n">
         <f aca="false">IF(Revenue!F$52=0,0,Revenue!F$48/Revenue!F$52)</f>
         <v>0.105762647843434</v>
       </c>
-      <c r="E11" s="29" t="n">
+      <c r="E11" s="31" t="n">
         <f aca="false">IF(Revenue!G$52=0,0,Revenue!G$48/Revenue!G$52)</f>
         <v>0.146294513955727</v>
       </c>
-      <c r="F11" s="29" t="n">
+      <c r="F11" s="31" t="n">
         <f aca="false">IF(Revenue!H$52=0,0,Revenue!H$48/Revenue!H$52)</f>
         <v>0.128702564587868</v>
       </c>
       <c r="G11" s="22"/>
       <c r="H11" s="22"/>
       <c r="I11" s="20" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2629,107 +2737,107 @@
         <v>0.0499668780164664</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="B13" s="29" t="n">
+      <c r="B13" s="31" t="n">
         <f aca="false">IF(Revenue!D$52=0,0,Revenue!D$50/Revenue!D$52)</f>
         <v>0</v>
       </c>
-      <c r="C13" s="29" t="n">
+      <c r="C13" s="31" t="n">
         <f aca="false">IF(Revenue!E$52=0,0,Revenue!E$50/Revenue!E$52)</f>
         <v>0.0140944326990839</v>
       </c>
-      <c r="D13" s="29" t="n">
+      <c r="D13" s="31" t="n">
         <f aca="false">IF(Revenue!F$52=0,0,Revenue!F$50/Revenue!F$52)</f>
         <v>0.025024197927241</v>
       </c>
-      <c r="E13" s="29" t="n">
+      <c r="E13" s="31" t="n">
         <f aca="false">IF(Revenue!G$52=0,0,Revenue!G$50/Revenue!G$52)</f>
         <v>0.0274989687886704</v>
       </c>
-      <c r="F13" s="29" t="n">
+      <c r="F13" s="31" t="n">
         <f aca="false">IF(Revenue!H$52=0,0,Revenue!H$50/Revenue!H$52)</f>
         <v>0.028390271600265</v>
       </c>
       <c r="G13" s="22"/>
       <c r="H13" s="22"/>
       <c r="I13" s="20" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>334</v>
-      </c>
-      <c r="B15" s="32" t="n">
+        <v>340</v>
+      </c>
+      <c r="B15" s="34" t="n">
         <f aca="false">SUM(B4:B13)</f>
         <v>1</v>
       </c>
-      <c r="C15" s="32" t="n">
+      <c r="C15" s="34" t="n">
         <f aca="false">SUM(C4:C13)</f>
         <v>1</v>
       </c>
-      <c r="D15" s="32" t="n">
+      <c r="D15" s="34" t="n">
         <f aca="false">SUM(D4:D13)</f>
         <v>1</v>
       </c>
-      <c r="E15" s="32" t="n">
+      <c r="E15" s="34" t="n">
         <f aca="false">SUM(E4:E13)</f>
         <v>1</v>
       </c>
-      <c r="F15" s="32" t="n">
+      <c r="F15" s="34" t="n">
         <f aca="false">SUM(F4:F13)</f>
         <v>1</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="33" t="s">
-        <v>337</v>
+        <v>342</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>338</v>
-      </c>
-      <c r="B21" s="34" t="n">
+        <v>344</v>
+      </c>
+      <c r="B21" s="24" t="n">
         <f aca="false">Pricing!$D$10</f>
         <v>15000000</v>
       </c>
-      <c r="C21" s="34" t="n">
+      <c r="C21" s="24" t="n">
         <f aca="false">Pricing!$D$10</f>
         <v>15000000</v>
       </c>
-      <c r="D21" s="34" t="n">
+      <c r="D21" s="24" t="n">
         <f aca="false">Pricing!$D$10</f>
         <v>15000000</v>
       </c>
-      <c r="E21" s="34" t="n">
+      <c r="E21" s="24" t="n">
         <f aca="false">Pricing!$D$10</f>
         <v>15000000</v>
       </c>
-      <c r="F21" s="34" t="n">
+      <c r="F21" s="24" t="n">
         <f aca="false">Pricing!$D$10</f>
         <v>15000000</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="B22" s="17" t="n">
         <f aca="false">IF(Revenue!D$52=0,0,B21/Revenue!D$52)</f>
@@ -2754,7 +2862,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="B23" s="35" t="str">
         <f aca="false">IF(B22&lt;=0.15,"Yes","NO")</f>
@@ -2778,255 +2886,255 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="27" t="s">
-        <v>341</v>
-      </c>
-      <c r="B25" s="27"/>
-      <c r="C25" s="27"/>
-      <c r="D25" s="27"/>
-      <c r="E25" s="27"/>
-      <c r="F25" s="27"/>
-      <c r="G25" s="27"/>
-      <c r="H25" s="27"/>
-      <c r="I25" s="27"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="36" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="37" t="s">
-        <v>343</v>
-      </c>
-      <c r="B28" s="38" t="s">
+      <c r="A25" s="29" t="s">
+        <v>347</v>
+      </c>
+      <c r="B25" s="29"/>
+      <c r="C25" s="29"/>
+      <c r="D25" s="29"/>
+      <c r="E25" s="29"/>
+      <c r="F25" s="29"/>
+      <c r="G25" s="29"/>
+      <c r="H25" s="29"/>
+      <c r="I25" s="29"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="4" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="36" t="s">
+        <v>349</v>
+      </c>
+      <c r="B28" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="C28" s="38" t="s">
+      <c r="C28" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="D28" s="38" t="s">
+      <c r="D28" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="E28" s="38" t="s">
+      <c r="E28" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="F28" s="38" t="s">
+      <c r="F28" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="G28" s="38"/>
-      <c r="H28" s="38" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="39" t="s">
+      <c r="G28" s="28"/>
+      <c r="H28" s="28" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="B29" s="40" t="n">
+      <c r="B29" s="17" t="n">
         <f aca="false">IF(Revenue!D$52=0,0,(Revenue!D$41)/Revenue!D$52)</f>
         <v>0.200401808136615</v>
       </c>
-      <c r="C29" s="40" t="n">
+      <c r="C29" s="17" t="n">
         <f aca="false">IF(Revenue!E$52=0,0,(Revenue!E$41)/Revenue!E$52)</f>
         <v>0.217289170777543</v>
       </c>
-      <c r="D29" s="40" t="n">
+      <c r="D29" s="17" t="n">
         <f aca="false">IF(Revenue!F$52=0,0,(Revenue!F$41)/Revenue!F$52)</f>
         <v>0.208338251611228</v>
       </c>
-      <c r="E29" s="40" t="n">
+      <c r="E29" s="17" t="n">
         <f aca="false">IF(Revenue!G$52=0,0,(Revenue!G$41)/Revenue!G$52)</f>
         <v>0.209267152481782</v>
       </c>
-      <c r="F29" s="40" t="n">
+      <c r="F29" s="17" t="n">
         <f aca="false">IF(Revenue!H$52=0,0,(Revenue!H$41)/Revenue!H$52)</f>
         <v>0.221160215766064</v>
       </c>
-      <c r="I29" s="33" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="39" t="s">
-        <v>345</v>
-      </c>
-      <c r="B30" s="40" t="n">
+      <c r="I29" s="3" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="B30" s="17" t="n">
         <f aca="false">IF(Revenue!D$52=0,0,(Revenue!D$43+Revenue!D$44)/Revenue!D$52)</f>
         <v>0.24108488196886</v>
       </c>
-      <c r="C30" s="40" t="n">
+      <c r="C30" s="17" t="n">
         <f aca="false">IF(Revenue!E$52=0,0,(Revenue!E$43+Revenue!E$44)/Revenue!E$52)</f>
         <v>0.251820530890298</v>
       </c>
-      <c r="D30" s="40" t="n">
+      <c r="D30" s="17" t="n">
         <f aca="false">IF(Revenue!F$52=0,0,(Revenue!F$43+Revenue!F$44)/Revenue!F$52)</f>
         <v>0.222715361552445</v>
       </c>
-      <c r="E30" s="40" t="n">
+      <c r="E30" s="17" t="n">
         <f aca="false">IF(Revenue!G$52=0,0,(Revenue!G$43+Revenue!G$44)/Revenue!G$52)</f>
         <v>0.191035336174893</v>
       </c>
-      <c r="F30" s="40" t="n">
+      <c r="F30" s="17" t="n">
         <f aca="false">IF(Revenue!H$52=0,0,(Revenue!H$43+Revenue!H$44)/Revenue!H$52)</f>
         <v>0.184347496924387</v>
       </c>
-      <c r="I30" s="33" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="39" t="s">
-        <v>347</v>
-      </c>
-      <c r="B31" s="40" t="n">
+      <c r="I30" s="3" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="B31" s="17" t="n">
         <f aca="false">IF(Revenue!D$52=0,0,(Revenue!D$45+Revenue!D$46)/Revenue!D$52)</f>
         <v>0.0763435459568056</v>
       </c>
-      <c r="C31" s="40" t="n">
+      <c r="C31" s="17" t="n">
         <f aca="false">IF(Revenue!E$52=0,0,(Revenue!E$45+Revenue!E$46)/Revenue!E$52)</f>
         <v>0.137185811604416</v>
       </c>
-      <c r="D31" s="40" t="n">
+      <c r="D31" s="17" t="n">
         <f aca="false">IF(Revenue!F$52=0,0,(Revenue!F$45+Revenue!F$46)/Revenue!F$52)</f>
         <v>0.1680870653226</v>
       </c>
-      <c r="E31" s="40" t="n">
+      <c r="E31" s="17" t="n">
         <f aca="false">IF(Revenue!G$52=0,0,(Revenue!G$45+Revenue!G$46)/Revenue!G$52)</f>
         <v>0.169668637426097</v>
       </c>
-      <c r="F31" s="40" t="n">
+      <c r="F31" s="17" t="n">
         <f aca="false">IF(Revenue!H$52=0,0,(Revenue!H$45+Revenue!H$46)/Revenue!H$52)</f>
         <v>0.18037285890035</v>
       </c>
-      <c r="I31" s="33" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="39" t="s">
+      <c r="I31" s="3" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="B32" s="40" t="n">
+      <c r="B32" s="17" t="n">
         <f aca="false">IF(Revenue!D$52=0,0,(Revenue!D$47)/Revenue!D$52)</f>
         <v>0.160723254645907</v>
       </c>
-      <c r="C32" s="40" t="n">
+      <c r="C32" s="17" t="n">
         <f aca="false">IF(Revenue!E$52=0,0,(Revenue!E$47)/Revenue!E$52)</f>
         <v>0.141883955837444</v>
       </c>
-      <c r="D32" s="40" t="n">
+      <c r="D32" s="17" t="n">
         <f aca="false">IF(Revenue!F$52=0,0,(Revenue!F$47)/Revenue!F$52)</f>
         <v>0.127481763025567</v>
       </c>
-      <c r="E32" s="40" t="n">
+      <c r="E32" s="17" t="n">
         <f aca="false">IF(Revenue!G$52=0,0,(Revenue!G$47)/Revenue!G$52)</f>
         <v>0.122535404922315</v>
       </c>
-      <c r="F32" s="40" t="n">
+      <c r="F32" s="17" t="n">
         <f aca="false">IF(Revenue!H$52=0,0,(Revenue!H$47)/Revenue!H$52)</f>
         <v>0.129081101542538</v>
       </c>
-      <c r="I32" s="33" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="39" t="s">
+      <c r="I32" s="3" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="B33" s="40" t="n">
+      <c r="B33" s="17" t="n">
         <f aca="false">IF(Revenue!D$52=0,0,(Revenue!D$48)/Revenue!D$52)</f>
         <v>0.12054244098443</v>
       </c>
-      <c r="C33" s="40" t="n">
+      <c r="C33" s="17" t="n">
         <f aca="false">IF(Revenue!E$52=0,0,(Revenue!E$48)/Revenue!E$52)</f>
         <v>0.105238430819826</v>
       </c>
-      <c r="D33" s="40" t="n">
+      <c r="D33" s="17" t="n">
         <f aca="false">IF(Revenue!F$52=0,0,(Revenue!F$48)/Revenue!F$52)</f>
         <v>0.105762647843434</v>
       </c>
-      <c r="E33" s="40" t="n">
+      <c r="E33" s="17" t="n">
         <f aca="false">IF(Revenue!G$52=0,0,(Revenue!G$48)/Revenue!G$52)</f>
         <v>0.146294513955727</v>
       </c>
-      <c r="F33" s="40" t="n">
+      <c r="F33" s="17" t="n">
         <f aca="false">IF(Revenue!H$52=0,0,(Revenue!H$48)/Revenue!H$52)</f>
         <v>0.128702564587868</v>
       </c>
-      <c r="I33" s="33" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="39" t="s">
+      <c r="I33" s="3" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="B34" s="40" t="n">
+      <c r="B34" s="17" t="n">
         <f aca="false">IF(Revenue!D$52=0,0,(Revenue!D$42)/Revenue!D$52)</f>
         <v>0.200904068307383</v>
       </c>
-      <c r="C34" s="40" t="n">
+      <c r="C34" s="17" t="n">
         <f aca="false">IF(Revenue!E$52=0,0,(Revenue!E$42)/Revenue!E$52)</f>
         <v>0.121212121212121</v>
       </c>
-      <c r="D34" s="40" t="n">
+      <c r="D34" s="17" t="n">
         <f aca="false">IF(Revenue!F$52=0,0,(Revenue!F$42)/Revenue!F$52)</f>
         <v>0.110484194622158</v>
       </c>
-      <c r="E34" s="40" t="n">
+      <c r="E34" s="17" t="n">
         <f aca="false">IF(Revenue!G$52=0,0,(Revenue!G$42)/Revenue!G$52)</f>
         <v>0.0893716485631789</v>
       </c>
-      <c r="F34" s="40" t="n">
+      <c r="F34" s="17" t="n">
         <f aca="false">IF(Revenue!H$52=0,0,(Revenue!H$42)/Revenue!H$52)</f>
         <v>0.0779786126620611</v>
       </c>
-      <c r="I34" s="33" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="39" t="s">
-        <v>348</v>
-      </c>
-      <c r="B35" s="40" t="n">
+      <c r="I34" s="3" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="5" t="s">
+        <v>354</v>
+      </c>
+      <c r="B35" s="17" t="n">
         <f aca="false">IF(Revenue!D$52=0,0,(Revenue!D$49+Revenue!D$50)/Revenue!D$52)</f>
         <v>0</v>
       </c>
-      <c r="C35" s="40" t="n">
+      <c r="C35" s="17" t="n">
         <f aca="false">IF(Revenue!E$52=0,0,(Revenue!E$49+Revenue!E$50)/Revenue!E$52)</f>
         <v>0.025369978858351</v>
       </c>
-      <c r="D35" s="40" t="n">
+      <c r="D35" s="17" t="n">
         <f aca="false">IF(Revenue!F$52=0,0,(Revenue!F$49+Revenue!F$50)/Revenue!F$52)</f>
         <v>0.057130716022569</v>
       </c>
-      <c r="E35" s="40" t="n">
+      <c r="E35" s="17" t="n">
         <f aca="false">IF(Revenue!G$52=0,0,(Revenue!G$49+Revenue!G$50)/Revenue!G$52)</f>
         <v>0.0718273064760071</v>
       </c>
-      <c r="F35" s="40" t="n">
+      <c r="F35" s="17" t="n">
         <f aca="false">IF(Revenue!H$52=0,0,(Revenue!H$49+Revenue!H$50)/Revenue!H$52)</f>
         <v>0.0783571496167313</v>
       </c>
-      <c r="I35" s="33" t="s">
-        <v>326</v>
+      <c r="I35" s="3" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="27" t="s">
-        <v>349</v>
-      </c>
-      <c r="B37" s="27"/>
-      <c r="C37" s="27"/>
-      <c r="D37" s="27"/>
-      <c r="E37" s="27"/>
-      <c r="F37" s="27"/>
-      <c r="G37" s="27"/>
-      <c r="H37" s="27"/>
-      <c r="I37" s="27"/>
+      <c r="A37" s="29" t="s">
+        <v>355</v>
+      </c>
+      <c r="B37" s="29"/>
+      <c r="C37" s="29"/>
+      <c r="D37" s="29"/>
+      <c r="E37" s="29"/>
+      <c r="F37" s="29"/>
+      <c r="G37" s="29"/>
+      <c r="H37" s="29"/>
+      <c r="I37" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3058,12 +3166,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3071,75 +3179,75 @@
         <v>78</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="B4" s="41" t="n">
+      <c r="B4" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="C4" s="41" t="n">
+      <c r="C4" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="D4" s="41" t="n">
+      <c r="D4" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="E4" s="41" t="n">
+      <c r="E4" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="F4" s="41" t="n">
+      <c r="F4" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="G4" s="41" t="n">
+      <c r="G4" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="H4" s="41" t="n">
+      <c r="H4" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="I4" s="41" t="n">
+      <c r="I4" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="J4" s="41" t="n">
+      <c r="J4" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="K4" s="28" t="n">
+      <c r="K4" s="30" t="n">
         <f aca="false">G4*((C4+E4)/2)*F4</f>
         <v>100</v>
       </c>
-      <c r="L4" s="42" t="n">
+      <c r="L4" s="37" t="n">
         <f aca="false">RANK(K4,$K$4:$K$13)</f>
         <v>2</v>
       </c>
@@ -3148,38 +3256,38 @@
       <c r="A5" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="B5" s="43" t="n">
+      <c r="B5" s="38" t="n">
         <v>4</v>
       </c>
-      <c r="C5" s="43" t="n">
+      <c r="C5" s="38" t="n">
         <v>4</v>
       </c>
-      <c r="D5" s="43" t="n">
+      <c r="D5" s="38" t="n">
         <v>3</v>
       </c>
-      <c r="E5" s="43" t="n">
+      <c r="E5" s="38" t="n">
         <v>5</v>
       </c>
-      <c r="F5" s="43" t="n">
+      <c r="F5" s="38" t="n">
         <v>3</v>
       </c>
-      <c r="G5" s="43" t="n">
+      <c r="G5" s="38" t="n">
         <v>5</v>
       </c>
-      <c r="H5" s="43" t="n">
+      <c r="H5" s="38" t="n">
         <v>2</v>
       </c>
-      <c r="I5" s="43" t="n">
+      <c r="I5" s="38" t="n">
         <v>3</v>
       </c>
-      <c r="J5" s="43" t="n">
+      <c r="J5" s="38" t="n">
         <v>4</v>
       </c>
-      <c r="K5" s="31" t="n">
+      <c r="K5" s="33" t="n">
         <f aca="false">G5*((C5+E5)/2)*F5</f>
         <v>67.5</v>
       </c>
-      <c r="L5" s="44" t="n">
+      <c r="L5" s="39" t="n">
         <f aca="false">RANK(K5,$K$4:$K$13)</f>
         <v>5</v>
       </c>
@@ -3188,38 +3296,38 @@
       <c r="A6" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="B6" s="41" t="n">
+      <c r="B6" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="C6" s="41" t="n">
+      <c r="C6" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="D6" s="41" t="n">
+      <c r="D6" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="E6" s="41" t="n">
+      <c r="E6" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="F6" s="41" t="n">
+      <c r="F6" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="G6" s="41" t="n">
+      <c r="G6" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="H6" s="41" t="n">
+      <c r="H6" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="I6" s="41" t="n">
+      <c r="I6" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="J6" s="41" t="n">
+      <c r="J6" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="K6" s="28" t="n">
+      <c r="K6" s="30" t="n">
         <f aca="false">G6*((C6+E6)/2)*F6</f>
         <v>56</v>
       </c>
-      <c r="L6" s="42" t="n">
+      <c r="L6" s="37" t="n">
         <f aca="false">RANK(K6,$K$4:$K$13)</f>
         <v>8</v>
       </c>
@@ -3228,38 +3336,38 @@
       <c r="A7" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="B7" s="43" t="n">
+      <c r="B7" s="38" t="n">
         <v>3</v>
       </c>
-      <c r="C7" s="43" t="n">
+      <c r="C7" s="38" t="n">
         <v>5</v>
       </c>
-      <c r="D7" s="43" t="n">
+      <c r="D7" s="38" t="n">
         <v>4</v>
       </c>
-      <c r="E7" s="43" t="n">
+      <c r="E7" s="38" t="n">
         <v>4</v>
       </c>
-      <c r="F7" s="43" t="n">
+      <c r="F7" s="38" t="n">
         <v>5</v>
       </c>
-      <c r="G7" s="43" t="n">
+      <c r="G7" s="38" t="n">
         <v>4</v>
       </c>
-      <c r="H7" s="43" t="n">
+      <c r="H7" s="38" t="n">
         <v>4</v>
       </c>
-      <c r="I7" s="43" t="n">
+      <c r="I7" s="38" t="n">
         <v>3</v>
       </c>
-      <c r="J7" s="43" t="n">
+      <c r="J7" s="38" t="n">
         <v>3</v>
       </c>
-      <c r="K7" s="31" t="n">
+      <c r="K7" s="33" t="n">
         <f aca="false">G7*((C7+E7)/2)*F7</f>
         <v>90</v>
       </c>
-      <c r="L7" s="44" t="n">
+      <c r="L7" s="39" t="n">
         <f aca="false">RANK(K7,$K$4:$K$13)</f>
         <v>3</v>
       </c>
@@ -3268,38 +3376,38 @@
       <c r="A8" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="B8" s="41" t="n">
+      <c r="B8" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="C8" s="41" t="n">
+      <c r="C8" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="D8" s="41" t="n">
+      <c r="D8" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="E8" s="41" t="n">
+      <c r="E8" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="F8" s="41" t="n">
+      <c r="F8" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="G8" s="41" t="n">
+      <c r="G8" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="H8" s="41" t="n">
+      <c r="H8" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="I8" s="41" t="n">
+      <c r="I8" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="J8" s="41" t="n">
+      <c r="J8" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="K8" s="28" t="n">
+      <c r="K8" s="30" t="n">
         <f aca="false">G8*((C8+E8)/2)*F8</f>
         <v>60</v>
       </c>
-      <c r="L8" s="42" t="n">
+      <c r="L8" s="37" t="n">
         <f aca="false">RANK(K8,$K$4:$K$13)</f>
         <v>6</v>
       </c>
@@ -3308,38 +3416,38 @@
       <c r="A9" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="B9" s="43" t="n">
+      <c r="B9" s="38" t="n">
         <v>4</v>
       </c>
-      <c r="C9" s="43" t="n">
+      <c r="C9" s="38" t="n">
         <v>4</v>
       </c>
-      <c r="D9" s="43" t="n">
+      <c r="D9" s="38" t="n">
         <v>5</v>
       </c>
-      <c r="E9" s="43" t="n">
+      <c r="E9" s="38" t="n">
         <v>5</v>
       </c>
-      <c r="F9" s="43" t="n">
+      <c r="F9" s="38" t="n">
         <v>5</v>
       </c>
-      <c r="G9" s="43" t="n">
+      <c r="G9" s="38" t="n">
         <v>5</v>
       </c>
-      <c r="H9" s="43" t="n">
+      <c r="H9" s="38" t="n">
         <v>4</v>
       </c>
-      <c r="I9" s="43" t="n">
+      <c r="I9" s="38" t="n">
         <v>2</v>
       </c>
-      <c r="J9" s="43" t="n">
+      <c r="J9" s="38" t="n">
         <v>2</v>
       </c>
-      <c r="K9" s="31" t="n">
+      <c r="K9" s="33" t="n">
         <f aca="false">G9*((C9+E9)/2)*F9</f>
         <v>112.5</v>
       </c>
-      <c r="L9" s="44" t="n">
+      <c r="L9" s="39" t="n">
         <f aca="false">RANK(K9,$K$4:$K$13)</f>
         <v>1</v>
       </c>
@@ -3348,38 +3456,38 @@
       <c r="A10" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="B10" s="41" t="n">
+      <c r="B10" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="C10" s="41" t="n">
+      <c r="C10" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="D10" s="41" t="n">
+      <c r="D10" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="E10" s="41" t="n">
+      <c r="E10" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="F10" s="41" t="n">
+      <c r="F10" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="G10" s="41" t="n">
+      <c r="G10" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="H10" s="41" t="n">
+      <c r="H10" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="I10" s="41" t="n">
+      <c r="I10" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="J10" s="41" t="n">
+      <c r="J10" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="K10" s="28" t="n">
+      <c r="K10" s="30" t="n">
         <f aca="false">G10*((C10+E10)/2)*F10</f>
         <v>18</v>
       </c>
-      <c r="L10" s="42" t="n">
+      <c r="L10" s="37" t="n">
         <f aca="false">RANK(K10,$K$4:$K$13)</f>
         <v>9</v>
       </c>
@@ -3388,38 +3496,38 @@
       <c r="A11" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="B11" s="43" t="n">
+      <c r="B11" s="38" t="n">
         <v>4</v>
       </c>
-      <c r="C11" s="43" t="n">
+      <c r="C11" s="38" t="n">
         <v>3</v>
       </c>
-      <c r="D11" s="43" t="n">
+      <c r="D11" s="38" t="n">
         <v>1</v>
       </c>
-      <c r="E11" s="43" t="n">
+      <c r="E11" s="38" t="n">
         <v>3</v>
       </c>
-      <c r="F11" s="43" t="n">
+      <c r="F11" s="38" t="n">
         <v>1</v>
       </c>
-      <c r="G11" s="43" t="n">
+      <c r="G11" s="38" t="n">
         <v>2</v>
       </c>
-      <c r="H11" s="43" t="n">
+      <c r="H11" s="38" t="n">
         <v>3</v>
       </c>
-      <c r="I11" s="43" t="n">
+      <c r="I11" s="38" t="n">
         <v>4</v>
       </c>
-      <c r="J11" s="43" t="n">
+      <c r="J11" s="38" t="n">
         <v>4</v>
       </c>
-      <c r="K11" s="31" t="n">
+      <c r="K11" s="33" t="n">
         <f aca="false">G11*((C11+E11)/2)*F11</f>
         <v>6</v>
       </c>
-      <c r="L11" s="44" t="n">
+      <c r="L11" s="39" t="n">
         <f aca="false">RANK(K11,$K$4:$K$13)</f>
         <v>10</v>
       </c>
@@ -3428,38 +3536,38 @@
       <c r="A12" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="B12" s="41" t="n">
+      <c r="B12" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="C12" s="41" t="n">
+      <c r="C12" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="D12" s="41" t="n">
+      <c r="D12" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="E12" s="41" t="n">
+      <c r="E12" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="F12" s="41" t="n">
+      <c r="F12" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="G12" s="41" t="n">
+      <c r="G12" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="H12" s="41" t="n">
+      <c r="H12" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="I12" s="41" t="n">
+      <c r="I12" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="J12" s="41" t="n">
+      <c r="J12" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="K12" s="28" t="n">
+      <c r="K12" s="30" t="n">
         <f aca="false">G12*((C12+E12)/2)*F12</f>
         <v>90</v>
       </c>
-      <c r="L12" s="42" t="n">
+      <c r="L12" s="37" t="n">
         <f aca="false">RANK(K12,$K$4:$K$13)</f>
         <v>3</v>
       </c>
@@ -3468,61 +3576,678 @@
       <c r="A13" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="B13" s="43" t="n">
+      <c r="B13" s="38" t="n">
         <v>3</v>
       </c>
-      <c r="C13" s="43" t="n">
+      <c r="C13" s="38" t="n">
         <v>3</v>
       </c>
-      <c r="D13" s="43" t="n">
+      <c r="D13" s="38" t="n">
         <v>5</v>
       </c>
-      <c r="E13" s="43" t="n">
+      <c r="E13" s="38" t="n">
         <v>5</v>
       </c>
-      <c r="F13" s="43" t="n">
+      <c r="F13" s="38" t="n">
         <v>5</v>
       </c>
-      <c r="G13" s="43" t="n">
+      <c r="G13" s="38" t="n">
         <v>3</v>
       </c>
-      <c r="H13" s="43" t="n">
+      <c r="H13" s="38" t="n">
         <v>4</v>
       </c>
-      <c r="I13" s="43" t="n">
+      <c r="I13" s="38" t="n">
         <v>1</v>
       </c>
-      <c r="J13" s="43" t="n">
+      <c r="J13" s="38" t="n">
         <v>2</v>
       </c>
-      <c r="K13" s="31" t="n">
+      <c r="K13" s="33" t="n">
         <f aca="false">G13*((C13+E13)/2)*F13</f>
         <v>60</v>
       </c>
-      <c r="L13" s="44" t="n">
+      <c r="L13" s="39" t="n">
         <f aca="false">RANK(K13,$K$4:$K$13)</f>
         <v>6</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="27" t="s">
-        <v>361</v>
-      </c>
-      <c r="B15" s="27"/>
-      <c r="C15" s="27"/>
-      <c r="D15" s="27"/>
-      <c r="E15" s="27"/>
-      <c r="F15" s="27"/>
-      <c r="G15" s="27"/>
-      <c r="H15" s="27"/>
-      <c r="I15" s="27"/>
-      <c r="J15" s="27"/>
-      <c r="K15" s="27"/>
-      <c r="L15" s="27"/>
+      <c r="A15" s="29" t="s">
+        <v>367</v>
+      </c>
+      <c r="B15" s="29"/>
+      <c r="C15" s="29"/>
+      <c r="D15" s="29"/>
+      <c r="E15" s="29"/>
+      <c r="F15" s="29"/>
+      <c r="G15" s="29"/>
+      <c r="H15" s="29"/>
+      <c r="I15" s="29"/>
+      <c r="J15" s="29"/>
+      <c r="K15" s="29"/>
+      <c r="L15" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A15:L15"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:H47"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="1" width="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="8"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="C6" s="24" t="n">
+        <f aca="false">SUMIFS(Revenue!$D$4:$D$38,Revenue!$J$4:$J$38,"VAACA")</f>
+        <v>158875000</v>
+      </c>
+      <c r="D6" s="24" t="n">
+        <f aca="false">SUMIFS(Revenue!$E$4:$E$38,Revenue!$J$4:$J$38,"VAACA")</f>
+        <v>342125000</v>
+      </c>
+      <c r="E6" s="24" t="n">
+        <f aca="false">SUMIFS(Revenue!$F$4:$F$38,Revenue!$J$4:$J$38,"VAACA")</f>
+        <v>686125000</v>
+      </c>
+      <c r="F6" s="24" t="n">
+        <f aca="false">SUMIFS(Revenue!$G$4:$G$38,Revenue!$J$4:$J$38,"VAACA")</f>
+        <v>1154900000</v>
+      </c>
+      <c r="G6" s="24" t="n">
+        <f aca="false">SUMIFS(Revenue!$H$4:$H$38,Revenue!$J$4:$J$38,"VAACA")</f>
+        <v>1739750000</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="C7" s="24" t="n">
+        <f aca="false">SUMIFS(Revenue!$D$4:$D$38,Revenue!$J$4:$J$38,"IAFN")</f>
+        <v>90000000</v>
+      </c>
+      <c r="D7" s="24" t="n">
+        <f aca="false">SUMIFS(Revenue!$E$4:$E$38,Revenue!$J$4:$J$38,"IAFN")</f>
+        <v>190000000</v>
+      </c>
+      <c r="E7" s="24" t="n">
+        <f aca="false">SUMIFS(Revenue!$F$4:$F$38,Revenue!$J$4:$J$38,"IAFN")</f>
+        <v>372850000</v>
+      </c>
+      <c r="F7" s="24" t="n">
+        <f aca="false">SUMIFS(Revenue!$G$4:$G$38,Revenue!$J$4:$J$38,"IAFN")</f>
+        <v>663350000</v>
+      </c>
+      <c r="G7" s="24" t="n">
+        <f aca="false">SUMIFS(Revenue!$H$4:$H$38,Revenue!$J$4:$J$38,"IAFN")</f>
+        <v>902000000</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="C8" s="27" t="n">
+        <f aca="false">C6+C7</f>
+        <v>248875000</v>
+      </c>
+      <c r="D8" s="27" t="n">
+        <f aca="false">D6+D7</f>
+        <v>532125000</v>
+      </c>
+      <c r="E8" s="27" t="n">
+        <f aca="false">E6+E7</f>
+        <v>1058975000</v>
+      </c>
+      <c r="F8" s="27" t="n">
+        <f aca="false">F6+F7</f>
+        <v>1818250000</v>
+      </c>
+      <c r="G8" s="27" t="n">
+        <f aca="false">G6+G7</f>
+        <v>2641750000</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="C9" s="17" t="n">
+        <f aca="false">IF(C8=0,0,C7/C8)</f>
+        <v>0.36162732295329</v>
+      </c>
+      <c r="D9" s="17" t="n">
+        <f aca="false">IF(D8=0,0,D7/D8)</f>
+        <v>0.357058961710125</v>
+      </c>
+      <c r="E9" s="17" t="n">
+        <f aca="false">IF(E8=0,0,E7/E8)</f>
+        <v>0.352085743289502</v>
+      </c>
+      <c r="F9" s="17" t="n">
+        <f aca="false">IF(F8=0,0,F7/F8)</f>
+        <v>0.364828818919291</v>
+      </c>
+      <c r="G9" s="17" t="n">
+        <f aca="false">IF(G8=0,0,G7/G8)</f>
+        <v>0.34144033311252</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="29" t="s">
+        <v>376</v>
+      </c>
+      <c r="B13" s="29"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="29"/>
+      <c r="E13" s="29"/>
+      <c r="F13" s="29"/>
+      <c r="G13" s="29"/>
+      <c r="H13" s="29"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="8"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="C16" s="16" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D16" s="16" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E16" s="16" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="F16" s="16" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G16" s="16" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="C17" s="21" t="n">
+        <f aca="false">C7*C16</f>
+        <v>10800000</v>
+      </c>
+      <c r="D17" s="21" t="n">
+        <f aca="false">D7*D16</f>
+        <v>22800000</v>
+      </c>
+      <c r="E17" s="21" t="n">
+        <f aca="false">E7*E16</f>
+        <v>44742000</v>
+      </c>
+      <c r="F17" s="21" t="n">
+        <f aca="false">F7*F16</f>
+        <v>79602000</v>
+      </c>
+      <c r="G17" s="21" t="n">
+        <f aca="false">G7*G16</f>
+        <v>108240000</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="C18" s="27" t="n">
+        <f aca="false">C6+C17</f>
+        <v>169675000</v>
+      </c>
+      <c r="D18" s="27" t="n">
+        <f aca="false">D6+D17</f>
+        <v>364925000</v>
+      </c>
+      <c r="E18" s="27" t="n">
+        <f aca="false">E6+E17</f>
+        <v>730867000</v>
+      </c>
+      <c r="F18" s="27" t="n">
+        <f aca="false">F6+F17</f>
+        <v>1234502000</v>
+      </c>
+      <c r="G18" s="27" t="n">
+        <f aca="false">G6+G17</f>
+        <v>1847990000</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="4" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="8"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="G22" s="9" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="6" t="s">
+        <v>381</v>
+      </c>
+      <c r="C23" s="27" t="n">
+        <f aca="false">C18</f>
+        <v>169675000</v>
+      </c>
+      <c r="D23" s="27" t="n">
+        <f aca="false">D18</f>
+        <v>364925000</v>
+      </c>
+      <c r="E23" s="27" t="n">
+        <f aca="false">E18</f>
+        <v>730867000</v>
+      </c>
+      <c r="F23" s="27" t="n">
+        <f aca="false">F18</f>
+        <v>1234502000</v>
+      </c>
+      <c r="G23" s="27" t="n">
+        <f aca="false">G18</f>
+        <v>1847990000</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="C24" s="21" t="n">
+        <f aca="false">-(Costs!C$7+Costs!C$9)</f>
+        <v>-27450000</v>
+      </c>
+      <c r="D24" s="21" t="n">
+        <f aca="false">-(Costs!D$7+Costs!D$9)</f>
+        <v>-51090000</v>
+      </c>
+      <c r="E24" s="21" t="n">
+        <f aca="false">-(Costs!E$7+Costs!E$9)</f>
+        <v>-92370000</v>
+      </c>
+      <c r="F24" s="21" t="n">
+        <f aca="false">-(Costs!F$7+Costs!F$9)</f>
+        <v>-146504000</v>
+      </c>
+      <c r="G24" s="21" t="n">
+        <f aca="false">-(Costs!G$7+Costs!G$9)</f>
+        <v>-217920000</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="C25" s="21" t="n">
+        <f aca="false">-SUMIFS(Staffing!$I$4:$I$15,Staffing!$O$4:$O$15,"VAACA")</f>
+        <v>-95160000</v>
+      </c>
+      <c r="D25" s="21" t="n">
+        <f aca="false">-SUMIFS(Staffing!$J$4:$J$15,Staffing!$O$4:$O$15,"VAACA")</f>
+        <v>-163968000</v>
+      </c>
+      <c r="E25" s="21" t="n">
+        <f aca="false">-SUMIFS(Staffing!$K$4:$K$15,Staffing!$O$4:$O$15,"VAACA")</f>
+        <v>-259128000</v>
+      </c>
+      <c r="F25" s="21" t="n">
+        <f aca="false">-SUMIFS(Staffing!$L$4:$L$15,Staffing!$O$4:$O$15,"VAACA")</f>
+        <v>-366000000</v>
+      </c>
+      <c r="G25" s="21" t="n">
+        <f aca="false">-SUMIFS(Staffing!$M$4:$M$15,Staffing!$O$4:$O$15,"VAACA")</f>
+        <v>-490440000</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="C26" s="21" t="n">
+        <f aca="false">-(Costs!C$17-Costs!C$18-Costs!C$4)</f>
+        <v>-103421250</v>
+      </c>
+      <c r="D26" s="21" t="n">
+        <f aca="false">-(Costs!D$17-Costs!D$18-Costs!D$4)</f>
+        <v>-185248750</v>
+      </c>
+      <c r="E26" s="21" t="n">
+        <f aca="false">-(Costs!E$17-Costs!E$18-Costs!E$4)</f>
+        <v>-301538500</v>
+      </c>
+      <c r="F26" s="21" t="n">
+        <f aca="false">-(Costs!F$17-Costs!F$18-Costs!F$4)</f>
+        <v>-442095000</v>
+      </c>
+      <c r="G26" s="21" t="n">
+        <f aca="false">-(Costs!G$17-Costs!G$18-Costs!G$4)</f>
+        <v>-552087500</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="C27" s="27" t="n">
+        <f aca="false">SUM(C23:C26)</f>
+        <v>-56356250</v>
+      </c>
+      <c r="D27" s="27" t="n">
+        <f aca="false">SUM(D23:D26)</f>
+        <v>-35381750</v>
+      </c>
+      <c r="E27" s="27" t="n">
+        <f aca="false">SUM(E23:E26)</f>
+        <v>77830500</v>
+      </c>
+      <c r="F27" s="27" t="n">
+        <f aca="false">SUM(F23:F26)</f>
+        <v>279903000</v>
+      </c>
+      <c r="G27" s="27" t="n">
+        <f aca="false">SUM(G23:G26)</f>
+        <v>587542500</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="C28" s="17" t="n">
+        <f aca="false">IF(C23=0,0,C27/C23)</f>
+        <v>-0.332142330926772</v>
+      </c>
+      <c r="D28" s="17" t="n">
+        <f aca="false">IF(D23=0,0,D27/D23)</f>
+        <v>-0.0969562238816195</v>
+      </c>
+      <c r="E28" s="17" t="n">
+        <f aca="false">IF(E23=0,0,E27/E23)</f>
+        <v>0.106490647409173</v>
+      </c>
+      <c r="F28" s="17" t="n">
+        <f aca="false">IF(F23=0,0,F27/F23)</f>
+        <v>0.226733533035993</v>
+      </c>
+      <c r="G28" s="17" t="n">
+        <f aca="false">IF(G23=0,0,G27/G23)</f>
+        <v>0.317935973679511</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="40" t="s">
+        <v>383</v>
+      </c>
+      <c r="C29" s="41" t="n">
+        <f aca="false">C27</f>
+        <v>-56356250</v>
+      </c>
+      <c r="D29" s="41" t="n">
+        <f aca="false">C29+D27</f>
+        <v>-91738000</v>
+      </c>
+      <c r="E29" s="41" t="n">
+        <f aca="false">D29+E27</f>
+        <v>-13907500</v>
+      </c>
+      <c r="F29" s="41" t="n">
+        <f aca="false">E29+F27</f>
+        <v>265995500</v>
+      </c>
+      <c r="G29" s="41" t="n">
+        <f aca="false">F29+G27</f>
+        <v>853538000</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="4" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="29" t="s">
+        <v>385</v>
+      </c>
+      <c r="B32" s="29"/>
+      <c r="C32" s="29"/>
+      <c r="D32" s="29"/>
+      <c r="E32" s="29"/>
+      <c r="F32" s="29"/>
+      <c r="G32" s="29"/>
+      <c r="H32" s="29"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="8"/>
+      <c r="B34" s="9"/>
+      <c r="C34" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E34" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="F34" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="G34" s="9" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="C35" s="17" t="n">
+        <f aca="false">IF(C18=0,0,C17/C18)</f>
+        <v>0.0636510976867541</v>
+      </c>
+      <c r="D35" s="17" t="n">
+        <f aca="false">IF(D18=0,0,D17/D18)</f>
+        <v>0.0624785914914023</v>
+      </c>
+      <c r="E35" s="17" t="n">
+        <f aca="false">IF(E18=0,0,E17/E18)</f>
+        <v>0.0612177044523833</v>
+      </c>
+      <c r="F35" s="17" t="n">
+        <f aca="false">IF(F18=0,0,F17/F18)</f>
+        <v>0.0644810619990895</v>
+      </c>
+      <c r="G35" s="17" t="n">
+        <f aca="false">IF(G18=0,0,G17/G18)</f>
+        <v>0.0585717455181035</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="C36" s="35" t="str">
+        <f aca="false">IF(C35&lt;=0.15,"Yes","NO")</f>
+        <v>Yes</v>
+      </c>
+      <c r="D36" s="35" t="str">
+        <f aca="false">IF(D35&lt;=0.15,"Yes","NO")</f>
+        <v>Yes</v>
+      </c>
+      <c r="E36" s="35" t="str">
+        <f aca="false">IF(E35&lt;=0.15,"Yes","NO")</f>
+        <v>Yes</v>
+      </c>
+      <c r="F36" s="35" t="str">
+        <f aca="false">IF(F35&lt;=0.15,"Yes","NO")</f>
+        <v>Yes</v>
+      </c>
+      <c r="G36" s="35" t="str">
+        <f aca="false">IF(G35&lt;=0.15,"Yes","NO")</f>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="29" t="s">
+        <v>387</v>
+      </c>
+      <c r="B38" s="29"/>
+      <c r="C38" s="29"/>
+      <c r="D38" s="29"/>
+      <c r="E38" s="29"/>
+      <c r="F38" s="29"/>
+      <c r="G38" s="29"/>
+      <c r="H38" s="29"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="42" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="43" t="s">
+        <v>389</v>
+      </c>
+      <c r="C42" s="44" t="n">
+        <f aca="false">MIN(C29:G29)</f>
+        <v>-91738000</v>
+      </c>
+      <c r="E42" s="45" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="40" t="s">
+        <v>391</v>
+      </c>
+      <c r="C43" s="41" t="n">
+        <f aca="false">IFERROR(MATCH(TRUE(),INDEX(C27:G27&gt;0,0),0),0)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="40" t="s">
+        <v>392</v>
+      </c>
+      <c r="C45" s="46" t="n">
+        <f aca="false">IF(D7=0,0,(-D24-D25-D26-D6)/D7)</f>
+        <v>0.306219736842105</v>
+      </c>
+      <c r="E45" s="45" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="57.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="29" t="s">
+        <v>394</v>
+      </c>
+      <c r="B47" s="29"/>
+      <c r="C47" s="29"/>
+      <c r="D47" s="29"/>
+      <c r="E47" s="29"/>
+      <c r="F47" s="29"/>
+      <c r="G47" s="29"/>
+      <c r="H47" s="29"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A32:H32"/>
+    <mergeCell ref="A38:H38"/>
+    <mergeCell ref="A47:H47"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -6964,13 +7689,15 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H57"/>
+  <dimension ref="A1:J59"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="44"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="4" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7008,6 +7735,9 @@
       <c r="H3" s="9" t="s">
         <v>42</v>
       </c>
+      <c r="J3" s="9" t="s">
+        <v>224</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
@@ -7039,6 +7769,9 @@
         <f aca="false">Customers!N4*Pricing!$D$4</f>
         <v>39375000</v>
       </c>
+      <c r="J4" s="25" t="s">
+        <v>225</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="18" t="s">
@@ -7050,25 +7783,28 @@
       <c r="C5" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="D5" s="25" t="n">
+      <c r="D5" s="26" t="n">
         <f aca="false">Customers!J5*Pricing!$D$5</f>
         <v>15750000</v>
       </c>
-      <c r="E5" s="25" t="n">
+      <c r="E5" s="26" t="n">
         <f aca="false">Customers!K5*Pricing!$D$5</f>
         <v>28875000</v>
       </c>
-      <c r="F5" s="25" t="n">
+      <c r="F5" s="26" t="n">
         <f aca="false">Customers!L5*Pricing!$D$5</f>
         <v>50750000</v>
       </c>
-      <c r="G5" s="25" t="n">
+      <c r="G5" s="26" t="n">
         <f aca="false">Customers!M5*Pricing!$D$5</f>
         <v>82250000</v>
       </c>
-      <c r="H5" s="25" t="n">
+      <c r="H5" s="26" t="n">
         <f aca="false">Customers!N5*Pricing!$D$5</f>
         <v>122500000</v>
+      </c>
+      <c r="J5" s="25" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7101,6 +7837,9 @@
         <f aca="false">Customers!N6*Pricing!$D$6</f>
         <v>88125000</v>
       </c>
+      <c r="J6" s="25" t="s">
+        <v>225</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="18" t="s">
@@ -7112,25 +7851,28 @@
       <c r="C7" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="D7" s="25" t="n">
+      <c r="D7" s="26" t="n">
         <f aca="false">Customers!J7*Pricing!$D$7</f>
         <v>13750000</v>
       </c>
-      <c r="E7" s="25" t="n">
+      <c r="E7" s="26" t="n">
         <f aca="false">Customers!K7*Pricing!$D$7</f>
         <v>28875000</v>
       </c>
-      <c r="F7" s="25" t="n">
+      <c r="F7" s="26" t="n">
         <f aca="false">Customers!L7*Pricing!$D$7</f>
         <v>55000000</v>
       </c>
-      <c r="G7" s="25" t="n">
+      <c r="G7" s="26" t="n">
         <f aca="false">Customers!M7*Pricing!$D$7</f>
         <v>90750000</v>
       </c>
-      <c r="H7" s="25" t="n">
+      <c r="H7" s="26" t="n">
         <f aca="false">Customers!N7*Pricing!$D$7</f>
         <v>140250000</v>
+      </c>
+      <c r="J7" s="25" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7163,6 +7905,9 @@
         <f aca="false">Customers!N8*Pricing!$D$8</f>
         <v>104000000</v>
       </c>
+      <c r="J8" s="25" t="s">
+        <v>225</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="18" t="s">
@@ -7174,25 +7919,28 @@
       <c r="C9" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="D9" s="25" t="n">
+      <c r="D9" s="26" t="n">
         <f aca="false">Customers!J9*Pricing!$D$9</f>
         <v>0</v>
       </c>
-      <c r="E9" s="25" t="n">
+      <c r="E9" s="26" t="n">
         <f aca="false">Customers!K9*Pricing!$D$9</f>
         <v>15000000</v>
       </c>
-      <c r="F9" s="25" t="n">
+      <c r="F9" s="26" t="n">
         <f aca="false">Customers!L9*Pricing!$D$9</f>
         <v>30000000</v>
       </c>
-      <c r="G9" s="25" t="n">
+      <c r="G9" s="26" t="n">
         <f aca="false">Customers!M9*Pricing!$D$9</f>
         <v>60000000</v>
       </c>
-      <c r="H9" s="25" t="n">
+      <c r="H9" s="26" t="n">
         <f aca="false">Customers!N9*Pricing!$D$9</f>
         <v>90000000</v>
+      </c>
+      <c r="J9" s="25" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7225,6 +7973,9 @@
         <f aca="false">Customers!N10*Pricing!$D$10</f>
         <v>90000000</v>
       </c>
+      <c r="J10" s="25" t="s">
+        <v>225</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="18" t="s">
@@ -7236,25 +7987,28 @@
       <c r="C11" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="D11" s="25" t="n">
+      <c r="D11" s="26" t="n">
         <f aca="false">Customers!J11*Pricing!$D$11</f>
         <v>20000000</v>
       </c>
-      <c r="E11" s="25" t="n">
+      <c r="E11" s="26" t="n">
         <f aca="false">Customers!K11*Pricing!$D$11</f>
         <v>30000000</v>
       </c>
-      <c r="F11" s="25" t="n">
+      <c r="F11" s="26" t="n">
         <f aca="false">Customers!L11*Pricing!$D$11</f>
         <v>45000000</v>
       </c>
-      <c r="G11" s="25" t="n">
+      <c r="G11" s="26" t="n">
         <f aca="false">Customers!M11*Pricing!$D$11</f>
         <v>65000000</v>
       </c>
-      <c r="H11" s="25" t="n">
+      <c r="H11" s="26" t="n">
         <f aca="false">Customers!N11*Pricing!$D$11</f>
         <v>80000000</v>
+      </c>
+      <c r="J11" s="25" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7287,6 +8041,9 @@
         <f aca="false">Customers!N12*Pricing!$D$12</f>
         <v>36000000</v>
       </c>
+      <c r="J12" s="25" t="s">
+        <v>225</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="18" t="s">
@@ -7298,25 +8055,28 @@
       <c r="C13" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="D13" s="25" t="n">
+      <c r="D13" s="26" t="n">
         <f aca="false">Customers!J13*Pricing!$D$13</f>
         <v>40000000</v>
       </c>
-      <c r="E13" s="25" t="n">
+      <c r="E13" s="26" t="n">
         <f aca="false">Customers!K13*Pricing!$D$13</f>
         <v>76000000</v>
       </c>
-      <c r="F13" s="25" t="n">
+      <c r="F13" s="26" t="n">
         <f aca="false">Customers!L13*Pricing!$D$13</f>
         <v>108000000</v>
       </c>
-      <c r="G13" s="25" t="n">
+      <c r="G13" s="26" t="n">
         <f aca="false">Customers!M13*Pricing!$D$13</f>
         <v>136000000</v>
       </c>
-      <c r="H13" s="25" t="n">
+      <c r="H13" s="26" t="n">
         <f aca="false">Customers!N13*Pricing!$D$13</f>
         <v>160000000</v>
+      </c>
+      <c r="J13" s="25" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7349,6 +8109,9 @@
         <f aca="false">Customers!N14*Pricing!$D$14</f>
         <v>100000000</v>
       </c>
+      <c r="J14" s="25" t="s">
+        <v>226</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="18" t="s">
@@ -7360,25 +8123,28 @@
       <c r="C15" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="D15" s="25" t="n">
+      <c r="D15" s="26" t="n">
         <f aca="false">Customers!J15*Pricing!$D$15</f>
         <v>0</v>
       </c>
-      <c r="E15" s="25" t="n">
+      <c r="E15" s="26" t="n">
         <f aca="false">Customers!K15*Pricing!$D$15</f>
         <v>0</v>
       </c>
-      <c r="F15" s="25" t="n">
+      <c r="F15" s="26" t="n">
         <f aca="false">Customers!L15*Pricing!$D$15</f>
         <v>20000000</v>
       </c>
-      <c r="G15" s="25" t="n">
+      <c r="G15" s="26" t="n">
         <f aca="false">Customers!M15*Pricing!$D$15</f>
         <v>40000000</v>
       </c>
-      <c r="H15" s="25" t="n">
+      <c r="H15" s="26" t="n">
         <f aca="false">Customers!N15*Pricing!$D$15</f>
         <v>80000000</v>
+      </c>
+      <c r="J15" s="25" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7411,6 +8177,9 @@
         <f aca="false">Customers!N16*Pricing!$D$16</f>
         <v>81000000</v>
       </c>
+      <c r="J16" s="25" t="s">
+        <v>226</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="18" t="s">
@@ -7422,25 +8191,28 @@
       <c r="C17" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="D17" s="25" t="n">
+      <c r="D17" s="26" t="n">
         <f aca="false">Customers!J17*Pricing!$D$17</f>
         <v>0</v>
       </c>
-      <c r="E17" s="25" t="n">
+      <c r="E17" s="26" t="n">
         <f aca="false">Customers!K17*Pricing!$D$17</f>
         <v>0</v>
       </c>
-      <c r="F17" s="25" t="n">
+      <c r="F17" s="26" t="n">
         <f aca="false">Customers!L17*Pricing!$D$17</f>
         <v>3600000</v>
       </c>
-      <c r="G17" s="25" t="n">
+      <c r="G17" s="26" t="n">
         <f aca="false">Customers!M17*Pricing!$D$17</f>
         <v>12600000</v>
       </c>
-      <c r="H17" s="25" t="n">
+      <c r="H17" s="26" t="n">
         <f aca="false">Customers!N17*Pricing!$D$17</f>
         <v>36000000</v>
+      </c>
+      <c r="J17" s="25" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7473,6 +8245,9 @@
         <f aca="false">Customers!N18*Pricing!$D$18</f>
         <v>30000000</v>
       </c>
+      <c r="J18" s="25" t="s">
+        <v>226</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="18" t="s">
@@ -7484,25 +8259,28 @@
       <c r="C19" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="D19" s="25" t="n">
+      <c r="D19" s="26" t="n">
         <f aca="false">Customers!J19*Pricing!$D$19</f>
         <v>12000000</v>
       </c>
-      <c r="E19" s="25" t="n">
+      <c r="E19" s="26" t="n">
         <f aca="false">Customers!K19*Pricing!$D$19</f>
         <v>24000000</v>
       </c>
-      <c r="F19" s="25" t="n">
+      <c r="F19" s="26" t="n">
         <f aca="false">Customers!L19*Pricing!$D$19</f>
         <v>42000000</v>
       </c>
-      <c r="G19" s="25" t="n">
+      <c r="G19" s="26" t="n">
         <f aca="false">Customers!M19*Pricing!$D$19</f>
         <v>63000000</v>
       </c>
-      <c r="H19" s="25" t="n">
+      <c r="H19" s="26" t="n">
         <f aca="false">Customers!N19*Pricing!$D$19</f>
         <v>90000000</v>
+      </c>
+      <c r="J19" s="25" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7535,6 +8313,9 @@
         <f aca="false">Customers!N20*Pricing!$D$20</f>
         <v>84000000</v>
       </c>
+      <c r="J20" s="25" t="s">
+        <v>225</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="18" t="s">
@@ -7546,25 +8327,28 @@
       <c r="C21" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="D21" s="25" t="n">
+      <c r="D21" s="26" t="n">
         <f aca="false">Customers!J21*Pricing!$D$21</f>
         <v>0</v>
       </c>
-      <c r="E21" s="25" t="n">
+      <c r="E21" s="26" t="n">
         <f aca="false">Customers!K21*Pricing!$D$21</f>
         <v>0</v>
       </c>
-      <c r="F21" s="25" t="n">
+      <c r="F21" s="26" t="n">
         <f aca="false">Customers!L21*Pricing!$D$21</f>
         <v>25000000</v>
       </c>
-      <c r="G21" s="25" t="n">
+      <c r="G21" s="26" t="n">
         <f aca="false">Customers!M21*Pricing!$D$21</f>
         <v>50000000</v>
       </c>
-      <c r="H21" s="25" t="n">
+      <c r="H21" s="26" t="n">
         <f aca="false">Customers!N21*Pricing!$D$21</f>
         <v>75000000</v>
+      </c>
+      <c r="J21" s="25" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7597,6 +8381,9 @@
         <f aca="false">Customers!N22*Pricing!$D$22</f>
         <v>50000000</v>
       </c>
+      <c r="J22" s="25" t="s">
+        <v>225</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="18" t="s">
@@ -7608,25 +8395,28 @@
       <c r="C23" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="D23" s="25" t="n">
+      <c r="D23" s="26" t="n">
         <f aca="false">Customers!J23*Pricing!$D$23</f>
         <v>0</v>
       </c>
-      <c r="E23" s="25" t="n">
+      <c r="E23" s="26" t="n">
         <f aca="false">Customers!K23*Pricing!$D$23</f>
         <v>9750000</v>
       </c>
-      <c r="F23" s="25" t="n">
+      <c r="F23" s="26" t="n">
         <f aca="false">Customers!L23*Pricing!$D$23</f>
         <v>22500000</v>
       </c>
-      <c r="G23" s="25" t="n">
+      <c r="G23" s="26" t="n">
         <f aca="false">Customers!M23*Pricing!$D$23</f>
         <v>41250000</v>
       </c>
-      <c r="H23" s="25" t="n">
+      <c r="H23" s="26" t="n">
         <f aca="false">Customers!N23*Pricing!$D$23</f>
         <v>67500000</v>
+      </c>
+      <c r="J23" s="25" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7659,6 +8449,9 @@
         <f aca="false">Customers!N24*Pricing!$D$24</f>
         <v>70000000</v>
       </c>
+      <c r="J24" s="25" t="s">
+        <v>225</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="18" t="s">
@@ -7670,25 +8463,28 @@
       <c r="C25" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="D25" s="25" t="n">
+      <c r="D25" s="26" t="n">
         <f aca="false">Customers!J25*Pricing!$D$25</f>
         <v>0</v>
       </c>
-      <c r="E25" s="25" t="n">
+      <c r="E25" s="26" t="n">
         <f aca="false">Customers!K25*Pricing!$D$25</f>
         <v>0</v>
       </c>
-      <c r="F25" s="25" t="n">
+      <c r="F25" s="26" t="n">
         <f aca="false">Customers!L25*Pricing!$D$25</f>
         <v>10000000</v>
       </c>
-      <c r="G25" s="25" t="n">
+      <c r="G25" s="26" t="n">
         <f aca="false">Customers!M25*Pricing!$D$25</f>
         <v>20000000</v>
       </c>
-      <c r="H25" s="25" t="n">
+      <c r="H25" s="26" t="n">
         <f aca="false">Customers!N25*Pricing!$D$25</f>
         <v>40000000</v>
+      </c>
+      <c r="J25" s="25" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7721,6 +8517,9 @@
         <f aca="false">Customers!N26*Pricing!$D$26</f>
         <v>0</v>
       </c>
+      <c r="J26" s="25" t="s">
+        <v>225</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="18" t="s">
@@ -7732,25 +8531,28 @@
       <c r="C27" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="D27" s="25" t="n">
+      <c r="D27" s="26" t="n">
         <f aca="false">Customers!J27*Pricing!$D$27</f>
         <v>15000000</v>
       </c>
-      <c r="E27" s="25" t="n">
+      <c r="E27" s="26" t="n">
         <f aca="false">Customers!K27*Pricing!$D$27</f>
         <v>24000000</v>
       </c>
-      <c r="F27" s="25" t="n">
+      <c r="F27" s="26" t="n">
         <f aca="false">Customers!L27*Pricing!$D$27</f>
         <v>36000000</v>
       </c>
-      <c r="G27" s="25" t="n">
+      <c r="G27" s="26" t="n">
         <f aca="false">Customers!M27*Pricing!$D$27</f>
         <v>52800000</v>
       </c>
-      <c r="H27" s="25" t="n">
+      <c r="H27" s="26" t="n">
         <f aca="false">Customers!N27*Pricing!$D$27</f>
         <v>75000000</v>
+      </c>
+      <c r="J27" s="25" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7783,6 +8585,9 @@
         <f aca="false">Customers!N28*Pricing!$D$28</f>
         <v>80000000</v>
       </c>
+      <c r="J28" s="25" t="s">
+        <v>225</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="18" t="s">
@@ -7794,25 +8599,28 @@
       <c r="C29" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="D29" s="25" t="n">
+      <c r="D29" s="26" t="n">
         <f aca="false">Customers!J29*Pricing!$D$29</f>
         <v>15000000</v>
       </c>
-      <c r="E29" s="25" t="n">
+      <c r="E29" s="26" t="n">
         <f aca="false">Customers!K29*Pricing!$D$29</f>
         <v>22500000</v>
       </c>
-      <c r="F29" s="25" t="n">
+      <c r="F29" s="26" t="n">
         <f aca="false">Customers!L29*Pricing!$D$29</f>
         <v>45000000</v>
       </c>
-      <c r="G29" s="25" t="n">
+      <c r="G29" s="26" t="n">
         <f aca="false">Customers!M29*Pricing!$D$29</f>
         <v>75000000</v>
       </c>
-      <c r="H29" s="25" t="n">
+      <c r="H29" s="26" t="n">
         <f aca="false">Customers!N29*Pricing!$D$29</f>
         <v>120000000</v>
+      </c>
+      <c r="J29" s="25" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7845,6 +8653,9 @@
         <f aca="false">Customers!N30*Pricing!$D$30</f>
         <v>66000000</v>
       </c>
+      <c r="J30" s="25" t="s">
+        <v>225</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="18" t="s">
@@ -7856,25 +8667,28 @@
       <c r="C31" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="D31" s="25" t="n">
+      <c r="D31" s="26" t="n">
         <f aca="false">Customers!J31*Pricing!$D$31</f>
         <v>12000000</v>
       </c>
-      <c r="E31" s="25" t="n">
+      <c r="E31" s="26" t="n">
         <f aca="false">Customers!K31*Pricing!$D$31</f>
         <v>20000000</v>
       </c>
-      <c r="F31" s="25" t="n">
+      <c r="F31" s="26" t="n">
         <f aca="false">Customers!L31*Pricing!$D$31</f>
         <v>40000000</v>
       </c>
-      <c r="G31" s="25" t="n">
+      <c r="G31" s="26" t="n">
         <f aca="false">Customers!M31*Pricing!$D$31</f>
         <v>60000000</v>
       </c>
-      <c r="H31" s="25" t="n">
+      <c r="H31" s="26" t="n">
         <f aca="false">Customers!N31*Pricing!$D$31</f>
         <v>80000000</v>
+      </c>
+      <c r="J31" s="25" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7907,6 +8721,9 @@
         <f aca="false">Customers!N32*Pricing!$D$32</f>
         <v>180000000</v>
       </c>
+      <c r="J32" s="25" t="s">
+        <v>226</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="18" t="s">
@@ -7918,25 +8735,28 @@
       <c r="C33" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="D33" s="25" t="n">
+      <c r="D33" s="26" t="n">
         <f aca="false">Customers!J33*Pricing!$D$33</f>
         <v>0</v>
       </c>
-      <c r="E33" s="25" t="n">
+      <c r="E33" s="26" t="n">
         <f aca="false">Customers!K33*Pricing!$D$33</f>
         <v>0</v>
       </c>
-      <c r="F33" s="25" t="n">
+      <c r="F33" s="26" t="n">
         <f aca="false">Customers!L33*Pricing!$D$33</f>
         <v>0</v>
       </c>
-      <c r="G33" s="25" t="n">
+      <c r="G33" s="26" t="n">
         <f aca="false">Customers!M33*Pricing!$D$33</f>
         <v>80000000</v>
       </c>
-      <c r="H33" s="25" t="n">
+      <c r="H33" s="26" t="n">
         <f aca="false">Customers!N33*Pricing!$D$33</f>
         <v>80000000</v>
+      </c>
+      <c r="J33" s="25" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7969,6 +8789,9 @@
         <f aca="false">Customers!N34*Pricing!$D$34</f>
         <v>54000000</v>
       </c>
+      <c r="J34" s="25" t="s">
+        <v>225</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="18" t="s">
@@ -7980,25 +8803,28 @@
       <c r="C35" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="D35" s="25" t="n">
+      <c r="D35" s="26" t="n">
         <f aca="false">Customers!J35*Pricing!$D$35</f>
         <v>0</v>
       </c>
-      <c r="E35" s="25" t="n">
+      <c r="E35" s="26" t="n">
         <f aca="false">Customers!K35*Pricing!$D$35</f>
         <v>0</v>
       </c>
-      <c r="F35" s="25" t="n">
+      <c r="F35" s="26" t="n">
         <f aca="false">Customers!L35*Pricing!$D$35</f>
         <v>16000000</v>
       </c>
-      <c r="G35" s="25" t="n">
+      <c r="G35" s="26" t="n">
         <f aca="false">Customers!M35*Pricing!$D$35</f>
         <v>32000000</v>
       </c>
-      <c r="H35" s="25" t="n">
+      <c r="H35" s="26" t="n">
         <f aca="false">Customers!N35*Pricing!$D$35</f>
         <v>48000000</v>
+      </c>
+      <c r="J35" s="25" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8031,6 +8857,9 @@
         <f aca="false">Customers!N36*Pricing!$D$36</f>
         <v>30000000</v>
       </c>
+      <c r="J36" s="25" t="s">
+        <v>225</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="18" t="s">
@@ -8042,25 +8871,28 @@
       <c r="C37" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="D37" s="25" t="n">
+      <c r="D37" s="26" t="n">
         <f aca="false">Customers!J37*Pricing!$D$37</f>
         <v>0</v>
       </c>
-      <c r="E37" s="25" t="n">
+      <c r="E37" s="26" t="n">
         <f aca="false">Customers!K37*Pricing!$D$37</f>
         <v>7500000</v>
       </c>
-      <c r="F37" s="25" t="n">
+      <c r="F37" s="26" t="n">
         <f aca="false">Customers!L37*Pricing!$D$37</f>
         <v>16500000</v>
       </c>
-      <c r="G37" s="25" t="n">
+      <c r="G37" s="26" t="n">
         <f aca="false">Customers!M37*Pricing!$D$37</f>
         <v>30000000</v>
       </c>
-      <c r="H37" s="25" t="n">
+      <c r="H37" s="26" t="n">
         <f aca="false">Customers!N37*Pricing!$D$37</f>
         <v>45000000</v>
+      </c>
+      <c r="J37" s="25" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8093,10 +8925,13 @@
         <f aca="false">Customers!N38*Pricing!$D$38</f>
         <v>30000000</v>
       </c>
+      <c r="J38" s="25" t="s">
+        <v>225</v>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8373,32 +9208,32 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="D52" s="26" t="n">
+        <v>228</v>
+      </c>
+      <c r="D52" s="27" t="n">
         <f aca="false">SUM(D41:D50)</f>
         <v>248875000</v>
       </c>
-      <c r="E52" s="26" t="n">
+      <c r="E52" s="27" t="n">
         <f aca="false">SUM(E41:E50)</f>
         <v>532125000</v>
       </c>
-      <c r="F52" s="26" t="n">
+      <c r="F52" s="27" t="n">
         <f aca="false">SUM(F41:F50)</f>
         <v>1058975000</v>
       </c>
-      <c r="G52" s="26" t="n">
+      <c r="G52" s="27" t="n">
         <f aca="false">SUM(G41:G50)</f>
         <v>1818250000</v>
       </c>
-      <c r="H52" s="26" t="n">
+      <c r="H52" s="27" t="n">
         <f aca="false">SUM(H41:H50)</f>
         <v>2641750000</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="5" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D54" s="14" t="n">
         <v>250000000</v>
@@ -8418,7 +9253,7 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="5" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="D55" s="17" t="n">
         <f aca="false">IF(D54=0,0,D52/D54-1)</f>
@@ -8443,7 +9278,12 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="3" t="s">
-        <v>228</v>
+        <v>231</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="3" t="s">
+        <v>232</v>
       </c>
     </row>
   </sheetData>
@@ -8462,7 +9302,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:O20"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="34"/>
@@ -8470,60 +9310,65 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="1" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="9" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="10"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="H3" s="9"/>
       <c r="I3" s="9" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="M3" s="9" t="s">
-        <v>242</v>
+        <v>246</v>
+      </c>
+      <c r="O3" s="28" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="B4" s="14" t="n">
         <v>21600000</v>
@@ -8563,10 +9408,13 @@
         <f aca="false">G4*$B4*(1+Assumptions!$C$35)</f>
         <v>26352000</v>
       </c>
+      <c r="O4" s="25" t="s">
+        <v>225</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="18" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="B5" s="19" t="n">
         <v>15600000</v>
@@ -8607,10 +9455,13 @@
         <f aca="false">G5*$B5*(1+Assumptions!$C$35)</f>
         <v>19032000</v>
       </c>
+      <c r="O5" s="25" t="s">
+        <v>225</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B6" s="14" t="n">
         <v>15600000</v>
@@ -8650,10 +9501,13 @@
         <f aca="false">G6*$B6*(1+Assumptions!$C$35)</f>
         <v>38064000</v>
       </c>
+      <c r="O6" s="25" t="s">
+        <v>225</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="18" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="B7" s="19" t="n">
         <v>14400000</v>
@@ -8694,10 +9548,13 @@
         <f aca="false">G7*$B7*(1+Assumptions!$C$35)</f>
         <v>35136000</v>
       </c>
+      <c r="O7" s="25" t="s">
+        <v>226</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="B8" s="14" t="n">
         <v>14400000</v>
@@ -8737,10 +9594,13 @@
         <f aca="false">G8*$B8*(1+Assumptions!$C$35)</f>
         <v>52704000</v>
       </c>
+      <c r="O8" s="25" t="s">
+        <v>225</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="18" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="B9" s="19" t="n">
         <v>10800000</v>
@@ -8781,10 +9641,13 @@
         <f aca="false">G9*$B9*(1+Assumptions!$C$35)</f>
         <v>39528000</v>
       </c>
+      <c r="O9" s="25" t="s">
+        <v>225</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="B10" s="14" t="n">
         <v>15600000</v>
@@ -8824,10 +9687,13 @@
         <f aca="false">G10*$B10*(1+Assumptions!$C$35)</f>
         <v>38064000</v>
       </c>
+      <c r="O10" s="25" t="s">
+        <v>225</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="18" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="B11" s="19" t="n">
         <v>10800000</v>
@@ -8868,10 +9734,13 @@
         <f aca="false">G11*$B11*(1+Assumptions!$C$35)</f>
         <v>26352000</v>
       </c>
+      <c r="O11" s="25" t="s">
+        <v>225</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="B12" s="14" t="n">
         <v>8400000</v>
@@ -8911,10 +9780,13 @@
         <f aca="false">G12*$B12*(1+Assumptions!$C$35)</f>
         <v>71736000</v>
       </c>
+      <c r="O12" s="25" t="s">
+        <v>225</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="18" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="B13" s="19" t="n">
         <v>13200000</v>
@@ -8955,10 +9827,13 @@
         <f aca="false">G13*$B13*(1+Assumptions!$C$35)</f>
         <v>64416000</v>
       </c>
+      <c r="O13" s="25" t="s">
+        <v>225</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="B14" s="14" t="n">
         <v>8400000</v>
@@ -8998,10 +9873,13 @@
         <f aca="false">G14*$B14*(1+Assumptions!$C$35)</f>
         <v>61488000</v>
       </c>
+      <c r="O14" s="25" t="s">
+        <v>225</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="18" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="B15" s="19" t="n">
         <v>7200000</v>
@@ -9042,58 +9920,66 @@
         <f aca="false">G15*$B15*(1+Assumptions!$C$35)</f>
         <v>52704000</v>
       </c>
+      <c r="O15" s="25" t="s">
+        <v>225</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="C17" s="26" t="n">
+        <v>261</v>
+      </c>
+      <c r="C17" s="27" t="n">
         <f aca="false">SUM(C4:C15)</f>
         <v>6</v>
       </c>
-      <c r="D17" s="26" t="n">
+      <c r="D17" s="27" t="n">
         <f aca="false">SUM(D4:D15)</f>
         <v>11</v>
       </c>
-      <c r="E17" s="26" t="n">
+      <c r="E17" s="27" t="n">
         <f aca="false">SUM(E4:E15)</f>
         <v>19</v>
       </c>
-      <c r="F17" s="26" t="n">
+      <c r="F17" s="27" t="n">
         <f aca="false">SUM(F4:F15)</f>
         <v>28</v>
       </c>
-      <c r="G17" s="26" t="n">
+      <c r="G17" s="27" t="n">
         <f aca="false">SUM(G4:G15)</f>
         <v>39</v>
       </c>
-      <c r="I17" s="26" t="n">
+      <c r="I17" s="27" t="n">
         <f aca="false">SUM(I4:I15)</f>
         <v>112728000</v>
       </c>
-      <c r="J17" s="26" t="n">
+      <c r="J17" s="27" t="n">
         <f aca="false">SUM(J4:J15)</f>
         <v>181536000</v>
       </c>
-      <c r="K17" s="26" t="n">
+      <c r="K17" s="27" t="n">
         <f aca="false">SUM(K4:K15)</f>
         <v>276696000</v>
       </c>
-      <c r="L17" s="26" t="n">
+      <c r="L17" s="27" t="n">
         <f aca="false">SUM(L4:L15)</f>
         <v>383568000</v>
       </c>
-      <c r="M17" s="26" t="n">
+      <c r="M17" s="27" t="n">
         <f aca="false">SUM(M4:M15)</f>
         <v>525576000</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>257</v>
+        <v>262</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3" t="s">
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -9122,17 +10008,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="B3" s="9" t="s">
         <v>45</v>
@@ -9155,10 +10041,10 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="C4" s="24" t="n">
         <f aca="false">Staffing!I$17</f>
@@ -9183,35 +10069,35 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="18" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="B5" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="C5" s="25" t="n">
+      <c r="C5" s="26" t="n">
         <f aca="false">Assumptions!C$18*Revenue!D$43</f>
         <v>22800000</v>
       </c>
-      <c r="D5" s="25" t="n">
+      <c r="D5" s="26" t="n">
         <f aca="false">Assumptions!D$18*Revenue!E$43</f>
         <v>41760000</v>
       </c>
-      <c r="E5" s="25" t="n">
+      <c r="E5" s="26" t="n">
         <f aca="false">Assumptions!E$18*Revenue!F$43</f>
         <v>63920000</v>
       </c>
-      <c r="F5" s="25" t="n">
+      <c r="F5" s="26" t="n">
         <f aca="false">Assumptions!F$18*Revenue!G$43</f>
         <v>84480000</v>
       </c>
-      <c r="G5" s="25" t="n">
+      <c r="G5" s="26" t="n">
         <f aca="false">Assumptions!G$18*Revenue!H$43</f>
         <v>108800000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>50</v>
@@ -9239,35 +10125,35 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="18" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="B7" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="C7" s="25" t="n">
+      <c r="C7" s="26" t="n">
         <f aca="false">Assumptions!C$20*Revenue!D$47</f>
         <v>20800000</v>
       </c>
-      <c r="D7" s="25" t="n">
+      <c r="D7" s="26" t="n">
         <f aca="false">Assumptions!D$20*Revenue!E$47</f>
         <v>36240000</v>
       </c>
-      <c r="E7" s="25" t="n">
+      <c r="E7" s="26" t="n">
         <f aca="false">Assumptions!E$20*Revenue!F$47</f>
         <v>60750000</v>
       </c>
-      <c r="F7" s="25" t="n">
+      <c r="F7" s="26" t="n">
         <f aca="false">Assumptions!F$20*Revenue!G$47</f>
         <v>95804000</v>
       </c>
-      <c r="G7" s="25" t="n">
+      <c r="G7" s="26" t="n">
         <f aca="false">Assumptions!G$20*Revenue!H$47</f>
         <v>143220000</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>54</v>
@@ -9295,28 +10181,28 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="18" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="B9" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="C9" s="25" t="n">
+      <c r="C9" s="26" t="n">
         <f aca="false">Assumptions!C$22*Revenue!D$45</f>
         <v>6650000</v>
       </c>
-      <c r="D9" s="25" t="n">
+      <c r="D9" s="26" t="n">
         <f aca="false">Assumptions!D$22*Revenue!E$45</f>
         <v>14850000</v>
       </c>
-      <c r="E9" s="25" t="n">
+      <c r="E9" s="26" t="n">
         <f aca="false">Assumptions!E$22*Revenue!F$45</f>
         <v>31620000</v>
       </c>
-      <c r="F9" s="25" t="n">
+      <c r="F9" s="26" t="n">
         <f aca="false">Assumptions!F$22*Revenue!G$45</f>
         <v>50700000</v>
       </c>
-      <c r="G9" s="25" t="n">
+      <c r="G9" s="26" t="n">
         <f aca="false">Assumptions!G$22*Revenue!H$45</f>
         <v>74700000</v>
       </c>
@@ -9354,25 +10240,25 @@
         <v>59</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>268</v>
-      </c>
-      <c r="C11" s="25" t="n">
+        <v>274</v>
+      </c>
+      <c r="C11" s="26" t="n">
         <f aca="false">Assumptions!C$24</f>
         <v>22000000</v>
       </c>
-      <c r="D11" s="25" t="n">
+      <c r="D11" s="26" t="n">
         <f aca="false">Assumptions!D$24</f>
         <v>38000000</v>
       </c>
-      <c r="E11" s="25" t="n">
+      <c r="E11" s="26" t="n">
         <f aca="false">Assumptions!E$24</f>
         <v>62000000</v>
       </c>
-      <c r="F11" s="25" t="n">
+      <c r="F11" s="26" t="n">
         <f aca="false">Assumptions!F$24</f>
         <v>85000000</v>
       </c>
-      <c r="G11" s="25" t="n">
+      <c r="G11" s="26" t="n">
         <f aca="false">Assumptions!G$24</f>
         <v>105000000</v>
       </c>
@@ -9382,7 +10268,7 @@
         <v>61</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="C12" s="24" t="n">
         <f aca="false">Assumptions!C$25</f>
@@ -9410,25 +10296,25 @@
         <v>62</v>
       </c>
       <c r="B13" s="20" t="s">
-        <v>268</v>
-      </c>
-      <c r="C13" s="25" t="n">
+        <v>274</v>
+      </c>
+      <c r="C13" s="26" t="n">
         <f aca="false">Assumptions!C$26</f>
         <v>24000000</v>
       </c>
-      <c r="D13" s="25" t="n">
+      <c r="D13" s="26" t="n">
         <f aca="false">Assumptions!D$26</f>
         <v>38000000</v>
       </c>
-      <c r="E13" s="25" t="n">
+      <c r="E13" s="26" t="n">
         <f aca="false">Assumptions!E$26</f>
         <v>58000000</v>
       </c>
-      <c r="F13" s="25" t="n">
+      <c r="F13" s="26" t="n">
         <f aca="false">Assumptions!F$26</f>
         <v>80000000</v>
       </c>
-      <c r="G13" s="25" t="n">
+      <c r="G13" s="26" t="n">
         <f aca="false">Assumptions!G$26</f>
         <v>100000000</v>
       </c>
@@ -9438,7 +10324,7 @@
         <v>63</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="C14" s="24" t="n">
         <f aca="false">Assumptions!C$27</f>
@@ -9466,57 +10352,57 @@
         <v>64</v>
       </c>
       <c r="B15" s="20" t="s">
-        <v>268</v>
-      </c>
-      <c r="C15" s="25" t="n">
+        <v>274</v>
+      </c>
+      <c r="C15" s="26" t="n">
         <f aca="false">Assumptions!C$28</f>
         <v>10000000</v>
       </c>
-      <c r="D15" s="25" t="n">
+      <c r="D15" s="26" t="n">
         <f aca="false">Assumptions!D$28</f>
         <v>26000000</v>
       </c>
-      <c r="E15" s="25" t="n">
+      <c r="E15" s="26" t="n">
         <f aca="false">Assumptions!E$28</f>
         <v>48000000</v>
       </c>
-      <c r="F15" s="25" t="n">
+      <c r="F15" s="26" t="n">
         <f aca="false">Assumptions!F$28</f>
         <v>72000000</v>
       </c>
-      <c r="G15" s="25" t="n">
+      <c r="G15" s="26" t="n">
         <f aca="false">Assumptions!G$28</f>
         <v>95000000</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>269</v>
-      </c>
-      <c r="C17" s="26" t="n">
+        <v>275</v>
+      </c>
+      <c r="C17" s="27" t="n">
         <f aca="false">SUM(C4:C15)</f>
         <v>279899250</v>
       </c>
-      <c r="D17" s="26" t="n">
+      <c r="D17" s="27" t="n">
         <f aca="false">SUM(D4:D15)</f>
         <v>491134750</v>
       </c>
-      <c r="E17" s="26" t="n">
+      <c r="E17" s="27" t="n">
         <f aca="false">SUM(E4:E15)</f>
         <v>798159500</v>
       </c>
-      <c r="F17" s="26" t="n">
+      <c r="F17" s="27" t="n">
         <f aca="false">SUM(F4:F15)</f>
         <v>1196605000</v>
       </c>
-      <c r="G17" s="26" t="n">
+      <c r="G17" s="27" t="n">
         <f aca="false">SUM(G4:G15)</f>
         <v>1585403500</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="C18" s="21" t="n">
         <f aca="false">SUM(C5:C9)</f>
@@ -9565,12 +10451,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9594,32 +10480,32 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>273</v>
-      </c>
-      <c r="C4" s="26" t="n">
+        <v>279</v>
+      </c>
+      <c r="C4" s="27" t="n">
         <f aca="false">Revenue!D$52</f>
         <v>248875000</v>
       </c>
-      <c r="D4" s="26" t="n">
+      <c r="D4" s="27" t="n">
         <f aca="false">Revenue!E$52</f>
         <v>532125000</v>
       </c>
-      <c r="E4" s="26" t="n">
+      <c r="E4" s="27" t="n">
         <f aca="false">Revenue!F$52</f>
         <v>1058975000</v>
       </c>
-      <c r="F4" s="26" t="n">
+      <c r="F4" s="27" t="n">
         <f aca="false">Revenue!G$52</f>
         <v>1818250000</v>
       </c>
-      <c r="G4" s="26" t="n">
+      <c r="G4" s="27" t="n">
         <f aca="false">Revenue!H$52</f>
         <v>2641750000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="C5" s="21" t="n">
         <f aca="false">-Costs!C$18</f>
@@ -9644,32 +10530,32 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>275</v>
-      </c>
-      <c r="C6" s="26" t="n">
+        <v>281</v>
+      </c>
+      <c r="C6" s="27" t="n">
         <f aca="false">C4+C5</f>
         <v>185125000</v>
       </c>
-      <c r="D6" s="26" t="n">
+      <c r="D6" s="27" t="n">
         <f aca="false">D4+D5</f>
         <v>407775000</v>
       </c>
-      <c r="E6" s="26" t="n">
+      <c r="E6" s="27" t="n">
         <f aca="false">E4+E5</f>
         <v>839050000</v>
       </c>
-      <c r="F6" s="26" t="n">
+      <c r="F6" s="27" t="n">
         <f aca="false">F4+F5</f>
         <v>1447308000</v>
       </c>
-      <c r="G6" s="26" t="n">
+      <c r="G6" s="27" t="n">
         <f aca="false">G4+G5</f>
         <v>2134010000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="C7" s="17" t="n">
         <f aca="false">IF(C4=0,0,C6/C4)</f>
@@ -9697,7 +10583,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="C9" s="21" t="n">
         <f aca="false">-Costs!C$4</f>
@@ -9722,7 +10608,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="C10" s="21" t="n">
         <f aca="false">-(Costs!C$17-Costs!C$18-Costs!C$4)</f>
@@ -9747,32 +10633,32 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="C11" s="26" t="n">
+        <v>284</v>
+      </c>
+      <c r="C11" s="27" t="n">
         <f aca="false">C6+C9+C10</f>
         <v>-31024250</v>
       </c>
-      <c r="D11" s="26" t="n">
+      <c r="D11" s="27" t="n">
         <f aca="false">D6+D9+D10</f>
         <v>40990250</v>
       </c>
-      <c r="E11" s="26" t="n">
+      <c r="E11" s="27" t="n">
         <f aca="false">E6+E9+E10</f>
         <v>260815500</v>
       </c>
-      <c r="F11" s="26" t="n">
+      <c r="F11" s="27" t="n">
         <f aca="false">F6+F9+F10</f>
         <v>621645000</v>
       </c>
-      <c r="G11" s="26" t="n">
+      <c r="G11" s="27" t="n">
         <f aca="false">G6+G9+G10</f>
         <v>1056346500</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="C12" s="17" t="n">
         <f aca="false">IF(C4=0,0,C11/C4)</f>
@@ -9800,7 +10686,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="C14" s="21" t="n">
         <f aca="false">Revenue!D$41+Revenue!D$46+Revenue!D$49+Revenue!D$50</f>
@@ -9825,7 +10711,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="C15" s="17" t="n">
         <f aca="false">IF(C4=0,0,C14/C4)</f>
@@ -9850,7 +10736,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="C16" s="21" t="n">
         <f aca="false">IF(Staffing!C$17=0,0,C4/Staffing!C$17)</f>
@@ -9875,12 +10761,12 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="C19" s="16" t="n">
         <v>0</v>
@@ -9900,7 +10786,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="C20" s="21" t="n">
         <f aca="false">-MAX(0,C11)*C19</f>
@@ -9925,40 +10811,40 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>286</v>
-      </c>
-      <c r="C21" s="26" t="n">
+        <v>292</v>
+      </c>
+      <c r="C21" s="27" t="n">
         <f aca="false">C11+C20</f>
         <v>-31024250</v>
       </c>
-      <c r="D21" s="26" t="n">
+      <c r="D21" s="27" t="n">
         <f aca="false">D11+D20</f>
         <v>24594150</v>
       </c>
-      <c r="E21" s="26" t="n">
+      <c r="E21" s="27" t="n">
         <f aca="false">E11+E20</f>
         <v>117366975</v>
       </c>
-      <c r="F21" s="26" t="n">
+      <c r="F21" s="27" t="n">
         <f aca="false">F11+F20</f>
         <v>248658000</v>
       </c>
-      <c r="G21" s="26" t="n">
+      <c r="G21" s="27" t="n">
         <f aca="false">G11+G20</f>
         <v>422538600</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="27" t="s">
-        <v>287</v>
-      </c>
-      <c r="B23" s="27"/>
-      <c r="C23" s="27"/>
-      <c r="D23" s="27"/>
-      <c r="E23" s="27"/>
-      <c r="F23" s="27"/>
-      <c r="G23" s="27"/>
-      <c r="H23" s="27"/>
+      <c r="A23" s="29" t="s">
+        <v>293</v>
+      </c>
+      <c r="B23" s="29"/>
+      <c r="C23" s="29"/>
+      <c r="D23" s="29"/>
+      <c r="E23" s="29"/>
+      <c r="F23" s="29"/>
+      <c r="G23" s="29"/>
+      <c r="H23" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -9988,202 +10874,202 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>290</v>
-      </c>
-      <c r="B4" s="26" t="n">
+        <v>296</v>
+      </c>
+      <c r="B4" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="26" t="n">
+      <c r="C4" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="D4" s="26" t="n">
+      <c r="D4" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="E4" s="26" t="n">
+      <c r="E4" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="F4" s="26" t="n">
+      <c r="F4" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="G4" s="26" t="n">
+      <c r="G4" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="H4" s="26" t="n">
+      <c r="H4" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="I4" s="26" t="n">
+      <c r="I4" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="J4" s="26" t="n">
+      <c r="J4" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="K4" s="26" t="n">
+      <c r="K4" s="27" t="n">
         <v>10</v>
       </c>
-      <c r="L4" s="26" t="n">
+      <c r="L4" s="27" t="n">
         <v>11</v>
       </c>
-      <c r="M4" s="26" t="n">
+      <c r="M4" s="27" t="n">
         <v>12</v>
       </c>
-      <c r="N4" s="26" t="n">
+      <c r="N4" s="27" t="n">
         <v>13</v>
       </c>
-      <c r="O4" s="26" t="n">
+      <c r="O4" s="27" t="n">
         <v>14</v>
       </c>
-      <c r="P4" s="26" t="n">
+      <c r="P4" s="27" t="n">
         <v>15</v>
       </c>
-      <c r="Q4" s="26" t="n">
+      <c r="Q4" s="27" t="n">
         <v>16</v>
       </c>
-      <c r="R4" s="26" t="n">
+      <c r="R4" s="27" t="n">
         <v>17</v>
       </c>
-      <c r="S4" s="26" t="n">
+      <c r="S4" s="27" t="n">
         <v>18</v>
       </c>
-      <c r="T4" s="26" t="n">
+      <c r="T4" s="27" t="n">
         <v>19</v>
       </c>
-      <c r="U4" s="26" t="n">
+      <c r="U4" s="27" t="n">
         <v>20</v>
       </c>
-      <c r="V4" s="26" t="n">
+      <c r="V4" s="27" t="n">
         <v>21</v>
       </c>
-      <c r="W4" s="26" t="n">
+      <c r="W4" s="27" t="n">
         <v>22</v>
       </c>
-      <c r="X4" s="26" t="n">
+      <c r="X4" s="27" t="n">
         <v>23</v>
       </c>
-      <c r="Y4" s="26" t="n">
+      <c r="Y4" s="27" t="n">
         <v>24</v>
       </c>
-      <c r="Z4" s="26" t="n">
+      <c r="Z4" s="27" t="n">
         <v>25</v>
       </c>
-      <c r="AA4" s="26" t="n">
+      <c r="AA4" s="27" t="n">
         <v>26</v>
       </c>
-      <c r="AB4" s="26" t="n">
+      <c r="AB4" s="27" t="n">
         <v>27</v>
       </c>
-      <c r="AC4" s="26" t="n">
+      <c r="AC4" s="27" t="n">
         <v>28</v>
       </c>
-      <c r="AD4" s="26" t="n">
+      <c r="AD4" s="27" t="n">
         <v>29</v>
       </c>
-      <c r="AE4" s="26" t="n">
+      <c r="AE4" s="27" t="n">
         <v>30</v>
       </c>
-      <c r="AF4" s="26" t="n">
+      <c r="AF4" s="27" t="n">
         <v>31</v>
       </c>
-      <c r="AG4" s="26" t="n">
+      <c r="AG4" s="27" t="n">
         <v>32</v>
       </c>
-      <c r="AH4" s="26" t="n">
+      <c r="AH4" s="27" t="n">
         <v>33</v>
       </c>
-      <c r="AI4" s="26" t="n">
+      <c r="AI4" s="27" t="n">
         <v>34</v>
       </c>
-      <c r="AJ4" s="26" t="n">
+      <c r="AJ4" s="27" t="n">
         <v>35</v>
       </c>
-      <c r="AK4" s="26" t="n">
+      <c r="AK4" s="27" t="n">
         <v>36</v>
       </c>
-      <c r="AL4" s="26" t="n">
+      <c r="AL4" s="27" t="n">
         <v>37</v>
       </c>
-      <c r="AM4" s="26" t="n">
+      <c r="AM4" s="27" t="n">
         <v>38</v>
       </c>
-      <c r="AN4" s="26" t="n">
+      <c r="AN4" s="27" t="n">
         <v>39</v>
       </c>
-      <c r="AO4" s="26" t="n">
+      <c r="AO4" s="27" t="n">
         <v>40</v>
       </c>
-      <c r="AP4" s="26" t="n">
+      <c r="AP4" s="27" t="n">
         <v>41</v>
       </c>
-      <c r="AQ4" s="26" t="n">
+      <c r="AQ4" s="27" t="n">
         <v>42</v>
       </c>
-      <c r="AR4" s="26" t="n">
+      <c r="AR4" s="27" t="n">
         <v>43</v>
       </c>
-      <c r="AS4" s="26" t="n">
+      <c r="AS4" s="27" t="n">
         <v>44</v>
       </c>
-      <c r="AT4" s="26" t="n">
+      <c r="AT4" s="27" t="n">
         <v>45</v>
       </c>
-      <c r="AU4" s="26" t="n">
+      <c r="AU4" s="27" t="n">
         <v>46</v>
       </c>
-      <c r="AV4" s="26" t="n">
+      <c r="AV4" s="27" t="n">
         <v>47</v>
       </c>
-      <c r="AW4" s="26" t="n">
+      <c r="AW4" s="27" t="n">
         <v>48</v>
       </c>
-      <c r="AX4" s="26" t="n">
+      <c r="AX4" s="27" t="n">
         <v>49</v>
       </c>
-      <c r="AY4" s="26" t="n">
+      <c r="AY4" s="27" t="n">
         <v>50</v>
       </c>
-      <c r="AZ4" s="26" t="n">
+      <c r="AZ4" s="27" t="n">
         <v>51</v>
       </c>
-      <c r="BA4" s="26" t="n">
+      <c r="BA4" s="27" t="n">
         <v>52</v>
       </c>
-      <c r="BB4" s="26" t="n">
+      <c r="BB4" s="27" t="n">
         <v>53</v>
       </c>
-      <c r="BC4" s="26" t="n">
+      <c r="BC4" s="27" t="n">
         <v>54</v>
       </c>
-      <c r="BD4" s="26" t="n">
+      <c r="BD4" s="27" t="n">
         <v>55</v>
       </c>
-      <c r="BE4" s="26" t="n">
+      <c r="BE4" s="27" t="n">
         <v>56</v>
       </c>
-      <c r="BF4" s="26" t="n">
+      <c r="BF4" s="27" t="n">
         <v>57</v>
       </c>
-      <c r="BG4" s="26" t="n">
+      <c r="BG4" s="27" t="n">
         <v>58</v>
       </c>
-      <c r="BH4" s="26" t="n">
+      <c r="BH4" s="27" t="n">
         <v>59</v>
       </c>
-      <c r="BI4" s="26" t="n">
+      <c r="BI4" s="27" t="n">
         <v>60</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="B5" s="3" t="n">
         <f aca="false">ROUNDUP(B4/12,0)</f>
@@ -10428,7 +11314,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="B6" s="3" t="n">
         <f aca="false">B4-12*(B5-1)</f>
@@ -10673,7 +11559,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13128,257 +14014,257 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="B19" s="26" t="n">
+        <v>228</v>
+      </c>
+      <c r="B19" s="27" t="n">
         <f aca="false">SUM(B9:B18)</f>
         <v>16322500</v>
       </c>
-      <c r="C19" s="26" t="n">
+      <c r="C19" s="27" t="n">
         <f aca="false">SUM(C9:C18)</f>
         <v>26827500</v>
       </c>
-      <c r="D19" s="26" t="n">
+      <c r="D19" s="27" t="n">
         <f aca="false">SUM(D9:D18)</f>
         <v>20510000</v>
       </c>
-      <c r="E19" s="26" t="n">
+      <c r="E19" s="27" t="n">
         <f aca="false">SUM(E9:E18)</f>
         <v>19612500</v>
       </c>
-      <c r="F19" s="26" t="n">
+      <c r="F19" s="27" t="n">
         <f aca="false">SUM(F9:F18)</f>
         <v>20792500</v>
       </c>
-      <c r="G19" s="26" t="n">
+      <c r="G19" s="27" t="n">
         <f aca="false">SUM(G9:G18)</f>
         <v>20293750</v>
       </c>
-      <c r="H19" s="26" t="n">
+      <c r="H19" s="27" t="n">
         <f aca="false">SUM(H9:H18)</f>
         <v>29313750</v>
       </c>
-      <c r="I19" s="26" t="n">
+      <c r="I19" s="27" t="n">
         <f aca="false">SUM(I9:I18)</f>
         <v>18513750</v>
       </c>
-      <c r="J19" s="26" t="n">
+      <c r="J19" s="27" t="n">
         <f aca="false">SUM(J9:J18)</f>
         <v>28392500</v>
       </c>
-      <c r="K19" s="26" t="n">
+      <c r="K19" s="27" t="n">
         <f aca="false">SUM(K9:K18)</f>
         <v>19992500</v>
       </c>
-      <c r="L19" s="26" t="n">
+      <c r="L19" s="27" t="n">
         <f aca="false">SUM(L9:L18)</f>
         <v>17391250</v>
       </c>
-      <c r="M19" s="26" t="n">
+      <c r="M19" s="27" t="n">
         <f aca="false">SUM(M9:M18)</f>
         <v>10912500</v>
       </c>
-      <c r="N19" s="26" t="n">
+      <c r="N19" s="27" t="n">
         <f aca="false">SUM(N9:N18)</f>
         <v>42587500</v>
       </c>
-      <c r="O19" s="26" t="n">
+      <c r="O19" s="27" t="n">
         <f aca="false">SUM(O9:O18)</f>
         <v>46227500</v>
       </c>
-      <c r="P19" s="26" t="n">
+      <c r="P19" s="27" t="n">
         <f aca="false">SUM(P9:P18)</f>
         <v>42620000</v>
       </c>
-      <c r="Q19" s="26" t="n">
+      <c r="Q19" s="27" t="n">
         <f aca="false">SUM(Q9:Q18)</f>
         <v>43292500</v>
       </c>
-      <c r="R19" s="26" t="n">
+      <c r="R19" s="27" t="n">
         <f aca="false">SUM(R9:R18)</f>
         <v>45702500</v>
       </c>
-      <c r="S19" s="26" t="n">
+      <c r="S19" s="27" t="n">
         <f aca="false">SUM(S9:S18)</f>
         <v>43716250</v>
       </c>
-      <c r="T19" s="26" t="n">
+      <c r="T19" s="27" t="n">
         <f aca="false">SUM(T9:T18)</f>
         <v>53946250</v>
       </c>
-      <c r="U19" s="26" t="n">
+      <c r="U19" s="27" t="n">
         <f aca="false">SUM(U9:U18)</f>
         <v>40186250</v>
       </c>
-      <c r="V19" s="26" t="n">
+      <c r="V19" s="27" t="n">
         <f aca="false">SUM(V9:V18)</f>
         <v>60632500</v>
       </c>
-      <c r="W19" s="26" t="n">
+      <c r="W19" s="27" t="n">
         <f aca="false">SUM(W9:W18)</f>
         <v>45192500</v>
       </c>
-      <c r="X19" s="26" t="n">
+      <c r="X19" s="27" t="n">
         <f aca="false">SUM(X9:X18)</f>
         <v>40753750</v>
       </c>
-      <c r="Y19" s="26" t="n">
+      <c r="Y19" s="27" t="n">
         <f aca="false">SUM(Y9:Y18)</f>
         <v>27267500</v>
       </c>
-      <c r="Z19" s="26" t="n">
+      <c r="Z19" s="27" t="n">
         <f aca="false">SUM(Z9:Z18)</f>
         <v>88887500</v>
       </c>
-      <c r="AA19" s="26" t="n">
+      <c r="AA19" s="27" t="n">
         <f aca="false">SUM(AA9:AA18)</f>
         <v>90992500</v>
       </c>
-      <c r="AB19" s="26" t="n">
+      <c r="AB19" s="27" t="n">
         <f aca="false">SUM(AB9:AB18)</f>
         <v>83982500</v>
       </c>
-      <c r="AC19" s="26" t="n">
+      <c r="AC19" s="27" t="n">
         <f aca="false">SUM(AC9:AC18)</f>
         <v>85769500</v>
       </c>
-      <c r="AD19" s="26" t="n">
+      <c r="AD19" s="27" t="n">
         <f aca="false">SUM(AD9:AD18)</f>
         <v>90509500</v>
       </c>
-      <c r="AE19" s="26" t="n">
+      <c r="AE19" s="27" t="n">
         <f aca="false">SUM(AE9:AE18)</f>
         <v>86969250</v>
       </c>
-      <c r="AF19" s="26" t="n">
+      <c r="AF19" s="27" t="n">
         <f aca="false">SUM(AF9:AF18)</f>
         <v>105233750</v>
       </c>
-      <c r="AG19" s="26" t="n">
+      <c r="AG19" s="27" t="n">
         <f aca="false">SUM(AG9:AG18)</f>
         <v>79989250</v>
       </c>
-      <c r="AH19" s="26" t="n">
+      <c r="AH19" s="27" t="n">
         <f aca="false">SUM(AH9:AH18)</f>
         <v>117409500</v>
       </c>
-      <c r="AI19" s="26" t="n">
+      <c r="AI19" s="27" t="n">
         <f aca="false">SUM(AI9:AI18)</f>
         <v>89726500</v>
       </c>
-      <c r="AJ19" s="26" t="n">
+      <c r="AJ19" s="27" t="n">
         <f aca="false">SUM(AJ9:AJ18)</f>
         <v>82062750</v>
       </c>
-      <c r="AK19" s="26" t="n">
+      <c r="AK19" s="27" t="n">
         <f aca="false">SUM(AK9:AK18)</f>
         <v>57442500</v>
       </c>
-      <c r="AL19" s="26" t="n">
+      <c r="AL19" s="27" t="n">
         <f aca="false">SUM(AL9:AL18)</f>
         <v>158642000</v>
       </c>
-      <c r="AM19" s="26" t="n">
+      <c r="AM19" s="27" t="n">
         <f aca="false">SUM(AM9:AM18)</f>
         <v>146889000</v>
       </c>
-      <c r="AN19" s="26" t="n">
+      <c r="AN19" s="27" t="n">
         <f aca="false">SUM(AN9:AN18)</f>
         <v>142177500</v>
       </c>
-      <c r="AO19" s="26" t="n">
+      <c r="AO19" s="27" t="n">
         <f aca="false">SUM(AO9:AO18)</f>
         <v>147733000</v>
       </c>
-      <c r="AP19" s="26" t="n">
+      <c r="AP19" s="27" t="n">
         <f aca="false">SUM(AP9:AP18)</f>
         <v>155569000</v>
       </c>
-      <c r="AQ19" s="26" t="n">
+      <c r="AQ19" s="27" t="n">
         <f aca="false">SUM(AQ9:AQ18)</f>
         <v>151238000</v>
       </c>
-      <c r="AR19" s="26" t="n">
+      <c r="AR19" s="27" t="n">
         <f aca="false">SUM(AR9:AR18)</f>
         <v>175425500</v>
       </c>
-      <c r="AS19" s="26" t="n">
+      <c r="AS19" s="27" t="n">
         <f aca="false">SUM(AS9:AS18)</f>
         <v>138082000</v>
       </c>
-      <c r="AT19" s="26" t="n">
+      <c r="AT19" s="27" t="n">
         <f aca="false">SUM(AT9:AT18)</f>
         <v>202199000</v>
       </c>
-      <c r="AU19" s="26" t="n">
+      <c r="AU19" s="27" t="n">
         <f aca="false">SUM(AU9:AU18)</f>
         <v>155674000</v>
       </c>
-      <c r="AV19" s="26" t="n">
+      <c r="AV19" s="27" t="n">
         <f aca="false">SUM(AV9:AV18)</f>
         <v>142958000</v>
       </c>
-      <c r="AW19" s="26" t="n">
+      <c r="AW19" s="27" t="n">
         <f aca="false">SUM(AW9:AW18)</f>
         <v>101663000</v>
       </c>
-      <c r="AX19" s="26" t="n">
+      <c r="AX19" s="27" t="n">
         <f aca="false">SUM(AX9:AX18)</f>
         <v>244175000</v>
       </c>
-      <c r="AY19" s="26" t="n">
+      <c r="AY19" s="27" t="n">
         <f aca="false">SUM(AY9:AY18)</f>
         <v>207445000</v>
       </c>
-      <c r="AZ19" s="26" t="n">
+      <c r="AZ19" s="27" t="n">
         <f aca="false">SUM(AZ9:AZ18)</f>
         <v>204210000</v>
       </c>
-      <c r="BA19" s="26" t="n">
+      <c r="BA19" s="27" t="n">
         <f aca="false">SUM(BA9:BA18)</f>
         <v>212935000</v>
       </c>
-      <c r="BB19" s="26" t="n">
+      <c r="BB19" s="27" t="n">
         <f aca="false">SUM(BB9:BB18)</f>
         <v>224735000</v>
       </c>
-      <c r="BC19" s="26" t="n">
+      <c r="BC19" s="27" t="n">
         <f aca="false">SUM(BC9:BC18)</f>
         <v>219872500</v>
       </c>
-      <c r="BD19" s="26" t="n">
+      <c r="BD19" s="27" t="n">
         <f aca="false">SUM(BD9:BD18)</f>
         <v>251742500</v>
       </c>
-      <c r="BE19" s="26" t="n">
+      <c r="BE19" s="27" t="n">
         <f aca="false">SUM(BE9:BE18)</f>
         <v>201272500</v>
       </c>
-      <c r="BF19" s="26" t="n">
+      <c r="BF19" s="27" t="n">
         <f aca="false">SUM(BF9:BF18)</f>
         <v>295615000</v>
       </c>
-      <c r="BG19" s="26" t="n">
+      <c r="BG19" s="27" t="n">
         <f aca="false">SUM(BG9:BG18)</f>
         <v>223515000</v>
       </c>
-      <c r="BH19" s="26" t="n">
+      <c r="BH19" s="27" t="n">
         <f aca="false">SUM(BH9:BH18)</f>
         <v>206877500</v>
       </c>
-      <c r="BI19" s="26" t="n">
+      <c r="BI19" s="27" t="n">
         <f aca="false">SUM(BI9:BI18)</f>
         <v>149355000</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="B21" s="21" t="n">
         <f aca="false">IF(B$4-Assumptions!$C$34&lt;1,0,INDEX($B$19:$BI$19,1,B$4-Assumptions!$C$34))</f>
@@ -13623,7 +14509,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="B22" s="21" t="n">
         <f aca="false">-(INDEX(Costs!$C$5:$G$5,1,B$5)*INDEX(Assumptions!$B$43:$M$43,1,B$6)+INDEX(Costs!$C$6:$G$6,1,B$5)*INDEX(Assumptions!$B$44:$M$44,1,B$6)+INDEX(Costs!$C$7:$G$7,1,B$5)*INDEX(Assumptions!$B$47:$M$47,1,B$6)+INDEX(Costs!$C$8:$G$8,1,B$5)*INDEX(Assumptions!$B$48:$M$48,1,B$6)+INDEX(Costs!$C$9:$G$9,1,B$5)*INDEX(Assumptions!$B$45:$M$45,1,B$6))</f>
@@ -13868,7 +14754,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="B23" s="21" t="n">
         <f aca="false">-(INDEX(Costs!$C$17:$G$17,1,B$5)-INDEX(Costs!$C$18:$G$18,1,B$5))/12</f>
@@ -14113,245 +14999,245 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>298</v>
-      </c>
-      <c r="B25" s="26" t="n">
+        <v>304</v>
+      </c>
+      <c r="B25" s="27" t="n">
         <f aca="false">B21+B22+B23</f>
         <v>-18548437.5</v>
       </c>
-      <c r="C25" s="26" t="n">
+      <c r="C25" s="27" t="n">
         <f aca="false">C21+C22+C23</f>
         <v>-3500937.5</v>
       </c>
-      <c r="D25" s="26" t="n">
+      <c r="D25" s="27" t="n">
         <f aca="false">D21+D22+D23</f>
         <v>4091062.5</v>
       </c>
-      <c r="E25" s="26" t="n">
+      <c r="E25" s="27" t="n">
         <f aca="false">E21+E22+E23</f>
         <v>-3368437.5</v>
       </c>
-      <c r="F25" s="26" t="n">
+      <c r="F25" s="27" t="n">
         <f aca="false">F21+F22+F23</f>
         <v>-4814937.5</v>
       </c>
-      <c r="G25" s="26" t="n">
+      <c r="G25" s="27" t="n">
         <f aca="false">G21+G22+G23</f>
         <v>-3970937.5</v>
       </c>
-      <c r="H25" s="26" t="n">
+      <c r="H25" s="27" t="n">
         <f aca="false">H21+H22+H23</f>
         <v>-4402687.5</v>
       </c>
-      <c r="I25" s="26" t="n">
+      <c r="I25" s="27" t="n">
         <f aca="false">I21+I22+I23</f>
         <v>5369312.5</v>
       </c>
-      <c r="J25" s="26" t="n">
+      <c r="J25" s="27" t="n">
         <f aca="false">J21+J22+J23</f>
         <v>-10343687.5</v>
       </c>
-      <c r="K25" s="26" t="n">
+      <c r="K25" s="27" t="n">
         <f aca="false">K21+K22+K23</f>
         <v>4071062.5</v>
       </c>
-      <c r="L25" s="26" t="n">
+      <c r="L25" s="27" t="n">
         <f aca="false">L21+L22+L23</f>
         <v>-3186937.5</v>
       </c>
-      <c r="M25" s="26" t="n">
+      <c r="M25" s="27" t="n">
         <f aca="false">M21+M22+M23</f>
         <v>-3331187.5</v>
       </c>
-      <c r="N25" s="26" t="n">
+      <c r="N25" s="27" t="n">
         <f aca="false">N21+N22+N23</f>
         <v>-20750895.8333333</v>
       </c>
-      <c r="O25" s="26" t="n">
+      <c r="O25" s="27" t="n">
         <f aca="false">O21+O22+O23</f>
         <v>8563104.16666667</v>
       </c>
-      <c r="P25" s="26" t="n">
+      <c r="P25" s="27" t="n">
         <f aca="false">P21+P22+P23</f>
         <v>6517504.16666667</v>
       </c>
-      <c r="Q25" s="26" t="n">
+      <c r="Q25" s="27" t="n">
         <f aca="false">Q21+Q22+Q23</f>
         <v>405004.166666668</v>
       </c>
-      <c r="R25" s="26" t="n">
+      <c r="R25" s="27" t="n">
         <f aca="false">R21+R22+R23</f>
         <v>55704.1666666679</v>
       </c>
-      <c r="S25" s="26" t="n">
+      <c r="S25" s="27" t="n">
         <f aca="false">S21+S22+S23</f>
         <v>2213704.16666667</v>
       </c>
-      <c r="T25" s="26" t="n">
+      <c r="T25" s="27" t="n">
         <f aca="false">T21+T22+T23</f>
         <v>713454.166666668</v>
       </c>
-      <c r="U25" s="26" t="n">
+      <c r="U25" s="27" t="n">
         <f aca="false">U21+U22+U23</f>
         <v>11983254.1666667</v>
       </c>
-      <c r="V25" s="26" t="n">
+      <c r="V25" s="27" t="n">
         <f aca="false">V21+V22+V23</f>
         <v>-10802545.8333333</v>
       </c>
-      <c r="W25" s="26" t="n">
+      <c r="W25" s="27" t="n">
         <f aca="false">W21+W22+W23</f>
         <v>17380104.1666667</v>
       </c>
-      <c r="X25" s="26" t="n">
+      <c r="X25" s="27" t="n">
         <f aca="false">X21+X22+X23</f>
         <v>4004104.16666667</v>
       </c>
-      <c r="Y25" s="26" t="n">
+      <c r="Y25" s="27" t="n">
         <f aca="false">Y21+Y22+Y23</f>
         <v>4352754.16666667</v>
       </c>
-      <c r="Z25" s="26" t="n">
+      <c r="Z25" s="27" t="n">
         <f aca="false">Z21+Z22+Z23</f>
         <v>-23169108.3333333</v>
       </c>
-      <c r="AA25" s="26" t="n">
+      <c r="AA25" s="27" t="n">
         <f aca="false">AA21+AA22+AA23</f>
         <v>34339491.6666667</v>
       </c>
-      <c r="AB25" s="26" t="n">
+      <c r="AB25" s="27" t="n">
         <f aca="false">AB21+AB22+AB23</f>
         <v>26794541.6666667</v>
       </c>
-      <c r="AC25" s="26" t="n">
+      <c r="AC25" s="27" t="n">
         <f aca="false">AC21+AC22+AC23</f>
         <v>15300691.6666667</v>
       </c>
-      <c r="AD25" s="26" t="n">
+      <c r="AD25" s="27" t="n">
         <f aca="false">AD21+AD22+AD23</f>
         <v>15240291.6666667</v>
       </c>
-      <c r="AE25" s="26" t="n">
+      <c r="AE25" s="27" t="n">
         <f aca="false">AE21+AE22+AE23</f>
         <v>19466291.6666667</v>
       </c>
-      <c r="AF25" s="26" t="n">
+      <c r="AF25" s="27" t="n">
         <f aca="false">AF21+AF22+AF23</f>
         <v>16886491.6666667</v>
       </c>
-      <c r="AG25" s="26" t="n">
+      <c r="AG25" s="27" t="n">
         <f aca="false">AG21+AG22+AG23</f>
         <v>37023541.6666667</v>
       </c>
-      <c r="AH25" s="26" t="n">
+      <c r="AH25" s="27" t="n">
         <f aca="false">AH21+AH22+AH23</f>
         <v>-3675558.33333334</v>
       </c>
-      <c r="AI25" s="26" t="n">
+      <c r="AI25" s="27" t="n">
         <f aca="false">AI21+AI22+AI23</f>
         <v>46759191.6666667</v>
       </c>
-      <c r="AJ25" s="26" t="n">
+      <c r="AJ25" s="27" t="n">
         <f aca="false">AJ21+AJ22+AJ23</f>
         <v>22555191.6666667</v>
       </c>
-      <c r="AK25" s="26" t="n">
+      <c r="AK25" s="27" t="n">
         <f aca="false">AK21+AK22+AK23</f>
         <v>23119441.6666667</v>
       </c>
-      <c r="AL25" s="26" t="n">
+      <c r="AL25" s="27" t="n">
         <f aca="false">AL21+AL22+AL23</f>
         <v>-15678350</v>
       </c>
-      <c r="AM25" s="26" t="n">
+      <c r="AM25" s="27" t="n">
         <f aca="false">AM21+AM22+AM23</f>
         <v>78613870</v>
       </c>
-      <c r="AN25" s="26" t="n">
+      <c r="AN25" s="27" t="n">
         <f aca="false">AN21+AN22+AN23</f>
         <v>51318290</v>
       </c>
-      <c r="AO25" s="26" t="n">
+      <c r="AO25" s="27" t="n">
         <f aca="false">AO21+AO22+AO23</f>
         <v>38923050</v>
       </c>
-      <c r="AP25" s="26" t="n">
+      <c r="AP25" s="27" t="n">
         <f aca="false">AP21+AP22+AP23</f>
         <v>41548470</v>
       </c>
-      <c r="AQ25" s="26" t="n">
+      <c r="AQ25" s="27" t="n">
         <f aca="false">AQ21+AQ22+AQ23</f>
         <v>48038550</v>
       </c>
-      <c r="AR25" s="26" t="n">
+      <c r="AR25" s="27" t="n">
         <f aca="false">AR21+AR22+AR23</f>
         <v>45407450</v>
       </c>
-      <c r="AS25" s="26" t="n">
+      <c r="AS25" s="27" t="n">
         <f aca="false">AS21+AS22+AS23</f>
         <v>73112730</v>
       </c>
-      <c r="AT25" s="26" t="n">
+      <c r="AT25" s="27" t="n">
         <f aca="false">AT21+AT22+AT23</f>
         <v>10449070</v>
       </c>
-      <c r="AU25" s="26" t="n">
+      <c r="AU25" s="27" t="n">
         <f aca="false">AU21+AU22+AU23</f>
         <v>95357870</v>
       </c>
-      <c r="AV25" s="26" t="n">
+      <c r="AV25" s="27" t="n">
         <f aca="false">AV21+AV22+AV23</f>
         <v>54726150</v>
       </c>
-      <c r="AW25" s="26" t="n">
+      <c r="AW25" s="27" t="n">
         <f aca="false">AW21+AW22+AW23</f>
         <v>55607350</v>
       </c>
-      <c r="AX25" s="26" t="n">
+      <c r="AX25" s="27" t="n">
         <f aca="false">AX21+AX22+AX23</f>
         <v>6013708.33333333</v>
       </c>
-      <c r="AY25" s="26" t="n">
+      <c r="AY25" s="27" t="n">
         <f aca="false">AY21+AY22+AY23</f>
         <v>139135308.333333</v>
       </c>
-      <c r="AZ25" s="26" t="n">
+      <c r="AZ25" s="27" t="n">
         <f aca="false">AZ21+AZ22+AZ23</f>
         <v>81719908.3333333</v>
       </c>
-      <c r="BA25" s="26" t="n">
+      <c r="BA25" s="27" t="n">
         <f aca="false">BA21+BA22+BA23</f>
         <v>67913108.3333333</v>
       </c>
-      <c r="BB25" s="26" t="n">
+      <c r="BB25" s="27" t="n">
         <f aca="false">BB21+BB22+BB23</f>
         <v>72279708.3333333</v>
       </c>
-      <c r="BC25" s="26" t="n">
+      <c r="BC25" s="27" t="n">
         <f aca="false">BC21+BC22+BC23</f>
         <v>81367308.3333333</v>
       </c>
-      <c r="BD25" s="26" t="n">
+      <c r="BD25" s="27" t="n">
         <f aca="false">BD21+BD22+BD23</f>
         <v>77760208.3333333</v>
       </c>
-      <c r="BE25" s="26" t="n">
+      <c r="BE25" s="27" t="n">
         <f aca="false">BE21+BE22+BE23</f>
         <v>115589208.333333</v>
       </c>
-      <c r="BF25" s="26" t="n">
+      <c r="BF25" s="27" t="n">
         <f aca="false">BF21+BF22+BF23</f>
         <v>29117208.3333333</v>
       </c>
-      <c r="BG25" s="26" t="n">
+      <c r="BG25" s="27" t="n">
         <f aca="false">BG21+BG22+BG23</f>
         <v>154892108.333333</v>
       </c>
-      <c r="BH25" s="26" t="n">
+      <c r="BH25" s="27" t="n">
         <f aca="false">BH21+BH22+BH23</f>
         <v>90688508.3333333</v>
       </c>
-      <c r="BI25" s="26" t="n">
+      <c r="BI25" s="27" t="n">
         <f aca="false">BI21+BI22+BI23</f>
         <v>92178208.3333333</v>
       </c>
@@ -14603,269 +15489,269 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="s">
-        <v>299</v>
-      </c>
-      <c r="B27" s="26" t="n">
+        <v>305</v>
+      </c>
+      <c r="B27" s="27" t="n">
         <f aca="false">B26+B25</f>
         <v>-18548437.5</v>
       </c>
-      <c r="C27" s="26" t="n">
+      <c r="C27" s="27" t="n">
         <f aca="false">C26+C25</f>
         <v>-22049375</v>
       </c>
-      <c r="D27" s="26" t="n">
+      <c r="D27" s="27" t="n">
         <f aca="false">D26+D25</f>
         <v>-17958312.5</v>
       </c>
-      <c r="E27" s="26" t="n">
+      <c r="E27" s="27" t="n">
         <f aca="false">E26+E25</f>
         <v>-21326750</v>
       </c>
-      <c r="F27" s="26" t="n">
+      <c r="F27" s="27" t="n">
         <f aca="false">F26+F25</f>
         <v>-26141687.5</v>
       </c>
-      <c r="G27" s="26" t="n">
+      <c r="G27" s="27" t="n">
         <f aca="false">G26+G25</f>
         <v>-30112625</v>
       </c>
-      <c r="H27" s="26" t="n">
+      <c r="H27" s="27" t="n">
         <f aca="false">H26+H25</f>
         <v>-34515312.5</v>
       </c>
-      <c r="I27" s="26" t="n">
+      <c r="I27" s="27" t="n">
         <f aca="false">I26+I25</f>
         <v>-29146000</v>
       </c>
-      <c r="J27" s="26" t="n">
+      <c r="J27" s="27" t="n">
         <f aca="false">J26+J25</f>
         <v>-39489687.5</v>
       </c>
-      <c r="K27" s="26" t="n">
+      <c r="K27" s="27" t="n">
         <f aca="false">K26+K25</f>
         <v>-35418625</v>
       </c>
-      <c r="L27" s="26" t="n">
+      <c r="L27" s="27" t="n">
         <f aca="false">L26+L25</f>
         <v>-38605562.5</v>
       </c>
-      <c r="M27" s="26" t="n">
+      <c r="M27" s="27" t="n">
         <f aca="false">M26+M25</f>
         <v>-41936750</v>
       </c>
-      <c r="N27" s="26" t="n">
+      <c r="N27" s="27" t="n">
         <f aca="false">N26+N25</f>
         <v>-62687645.8333333</v>
       </c>
-      <c r="O27" s="26" t="n">
+      <c r="O27" s="27" t="n">
         <f aca="false">O26+O25</f>
         <v>-54124541.6666667</v>
       </c>
-      <c r="P27" s="26" t="n">
+      <c r="P27" s="27" t="n">
         <f aca="false">P26+P25</f>
         <v>-47607037.5</v>
       </c>
-      <c r="Q27" s="26" t="n">
+      <c r="Q27" s="27" t="n">
         <f aca="false">Q26+Q25</f>
         <v>-47202033.3333333</v>
       </c>
-      <c r="R27" s="26" t="n">
+      <c r="R27" s="27" t="n">
         <f aca="false">R26+R25</f>
         <v>-47146329.1666666</v>
       </c>
-      <c r="S27" s="26" t="n">
+      <c r="S27" s="27" t="n">
         <f aca="false">S26+S25</f>
         <v>-44932625</v>
       </c>
-      <c r="T27" s="26" t="n">
+      <c r="T27" s="27" t="n">
         <f aca="false">T26+T25</f>
         <v>-44219170.8333333</v>
       </c>
-      <c r="U27" s="26" t="n">
+      <c r="U27" s="27" t="n">
         <f aca="false">U26+U25</f>
         <v>-32235916.6666666</v>
       </c>
-      <c r="V27" s="26" t="n">
+      <c r="V27" s="27" t="n">
         <f aca="false">V26+V25</f>
         <v>-43038462.5</v>
       </c>
-      <c r="W27" s="26" t="n">
+      <c r="W27" s="27" t="n">
         <f aca="false">W26+W25</f>
         <v>-25658358.3333333</v>
       </c>
-      <c r="X27" s="26" t="n">
+      <c r="X27" s="27" t="n">
         <f aca="false">X26+X25</f>
         <v>-21654254.1666666</v>
       </c>
-      <c r="Y27" s="26" t="n">
+      <c r="Y27" s="27" t="n">
         <f aca="false">Y26+Y25</f>
         <v>-17301500</v>
       </c>
-      <c r="Z27" s="26" t="n">
+      <c r="Z27" s="27" t="n">
         <f aca="false">Z26+Z25</f>
         <v>-40470608.3333333</v>
       </c>
-      <c r="AA27" s="26" t="n">
+      <c r="AA27" s="27" t="n">
         <f aca="false">AA26+AA25</f>
         <v>-6131116.66666663</v>
       </c>
-      <c r="AB27" s="26" t="n">
+      <c r="AB27" s="27" t="n">
         <f aca="false">AB26+AB25</f>
         <v>20663425</v>
       </c>
-      <c r="AC27" s="26" t="n">
+      <c r="AC27" s="27" t="n">
         <f aca="false">AC26+AC25</f>
         <v>35964116.6666667</v>
       </c>
-      <c r="AD27" s="26" t="n">
+      <c r="AD27" s="27" t="n">
         <f aca="false">AD26+AD25</f>
         <v>51204408.3333334</v>
       </c>
-      <c r="AE27" s="26" t="n">
+      <c r="AE27" s="27" t="n">
         <f aca="false">AE26+AE25</f>
         <v>70670700</v>
       </c>
-      <c r="AF27" s="26" t="n">
+      <c r="AF27" s="27" t="n">
         <f aca="false">AF26+AF25</f>
         <v>87557191.6666667</v>
       </c>
-      <c r="AG27" s="26" t="n">
+      <c r="AG27" s="27" t="n">
         <f aca="false">AG26+AG25</f>
         <v>124580733.333333</v>
       </c>
-      <c r="AH27" s="26" t="n">
+      <c r="AH27" s="27" t="n">
         <f aca="false">AH26+AH25</f>
         <v>120905175</v>
       </c>
-      <c r="AI27" s="26" t="n">
+      <c r="AI27" s="27" t="n">
         <f aca="false">AI26+AI25</f>
         <v>167664366.666667</v>
       </c>
-      <c r="AJ27" s="26" t="n">
+      <c r="AJ27" s="27" t="n">
         <f aca="false">AJ26+AJ25</f>
         <v>190219558.333333</v>
       </c>
-      <c r="AK27" s="26" t="n">
+      <c r="AK27" s="27" t="n">
         <f aca="false">AK26+AK25</f>
         <v>213339000</v>
       </c>
-      <c r="AL27" s="26" t="n">
+      <c r="AL27" s="27" t="n">
         <f aca="false">AL26+AL25</f>
         <v>197660650</v>
       </c>
-      <c r="AM27" s="26" t="n">
+      <c r="AM27" s="27" t="n">
         <f aca="false">AM26+AM25</f>
         <v>276274520</v>
       </c>
-      <c r="AN27" s="26" t="n">
+      <c r="AN27" s="27" t="n">
         <f aca="false">AN26+AN25</f>
         <v>327592810</v>
       </c>
-      <c r="AO27" s="26" t="n">
+      <c r="AO27" s="27" t="n">
         <f aca="false">AO26+AO25</f>
         <v>366515860</v>
       </c>
-      <c r="AP27" s="26" t="n">
+      <c r="AP27" s="27" t="n">
         <f aca="false">AP26+AP25</f>
         <v>408064330</v>
       </c>
-      <c r="AQ27" s="26" t="n">
+      <c r="AQ27" s="27" t="n">
         <f aca="false">AQ26+AQ25</f>
         <v>456102880</v>
       </c>
-      <c r="AR27" s="26" t="n">
+      <c r="AR27" s="27" t="n">
         <f aca="false">AR26+AR25</f>
         <v>501510330</v>
       </c>
-      <c r="AS27" s="26" t="n">
+      <c r="AS27" s="27" t="n">
         <f aca="false">AS26+AS25</f>
         <v>574623060</v>
       </c>
-      <c r="AT27" s="26" t="n">
+      <c r="AT27" s="27" t="n">
         <f aca="false">AT26+AT25</f>
         <v>585072130</v>
       </c>
-      <c r="AU27" s="26" t="n">
+      <c r="AU27" s="27" t="n">
         <f aca="false">AU26+AU25</f>
         <v>680430000</v>
       </c>
-      <c r="AV27" s="26" t="n">
+      <c r="AV27" s="27" t="n">
         <f aca="false">AV26+AV25</f>
         <v>735156150</v>
       </c>
-      <c r="AW27" s="26" t="n">
+      <c r="AW27" s="27" t="n">
         <f aca="false">AW26+AW25</f>
         <v>790763500</v>
       </c>
-      <c r="AX27" s="26" t="n">
+      <c r="AX27" s="27" t="n">
         <f aca="false">AX26+AX25</f>
         <v>796777208.333333</v>
       </c>
-      <c r="AY27" s="26" t="n">
+      <c r="AY27" s="27" t="n">
         <f aca="false">AY26+AY25</f>
         <v>935912516.666667</v>
       </c>
-      <c r="AZ27" s="26" t="n">
+      <c r="AZ27" s="27" t="n">
         <f aca="false">AZ26+AZ25</f>
         <v>1017632425</v>
       </c>
-      <c r="BA27" s="26" t="n">
+      <c r="BA27" s="27" t="n">
         <f aca="false">BA26+BA25</f>
         <v>1085545533.33333</v>
       </c>
-      <c r="BB27" s="26" t="n">
+      <c r="BB27" s="27" t="n">
         <f aca="false">BB26+BB25</f>
         <v>1157825241.66667</v>
       </c>
-      <c r="BC27" s="26" t="n">
+      <c r="BC27" s="27" t="n">
         <f aca="false">BC26+BC25</f>
         <v>1239192550</v>
       </c>
-      <c r="BD27" s="26" t="n">
+      <c r="BD27" s="27" t="n">
         <f aca="false">BD26+BD25</f>
         <v>1316952758.33333</v>
       </c>
-      <c r="BE27" s="26" t="n">
+      <c r="BE27" s="27" t="n">
         <f aca="false">BE26+BE25</f>
         <v>1432541966.66667</v>
       </c>
-      <c r="BF27" s="26" t="n">
+      <c r="BF27" s="27" t="n">
         <f aca="false">BF26+BF25</f>
         <v>1461659175</v>
       </c>
-      <c r="BG27" s="26" t="n">
+      <c r="BG27" s="27" t="n">
         <f aca="false">BG26+BG25</f>
         <v>1616551283.33333</v>
       </c>
-      <c r="BH27" s="26" t="n">
+      <c r="BH27" s="27" t="n">
         <f aca="false">BH26+BH25</f>
         <v>1707239791.66667</v>
       </c>
-      <c r="BI27" s="26" t="n">
+      <c r="BI27" s="27" t="n">
         <f aca="false">BI26+BI25</f>
         <v>1799418000</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>301</v>
-      </c>
-      <c r="B30" s="26" t="n">
+        <v>307</v>
+      </c>
+      <c r="B30" s="27" t="n">
         <f aca="false">MIN($B$27:$BI$27)</f>
         <v>-62687645.8333333</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="B31" s="21" t="n">
         <f aca="false">MATCH(B30,$B$27:$BI$27,0)</f>
@@ -14874,7 +15760,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="B32" s="21" t="n">
         <f aca="false">IFERROR(MATCH(TRUE(),INDEX($B$27:$BI$27&gt;0,0),0),0)</f>
@@ -14883,7 +15769,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="B33" s="21" t="n">
         <f aca="false">SUM($B$21:$M$21)</f>
@@ -14892,7 +15778,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="B34" s="21" t="n">
         <f aca="false">-SUM($B$22:$M$22)-SUM($B$23:$M$23)</f>
